--- a/tests/ev_test_report.xlsx
+++ b/tests/ev_test_report.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13 13:42:08</t>
+          <t>2026-06-16 21:19:10</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>prabha.testuser@example.com</t>
+          <t>prabha02102005@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>html_len=93765</t>
+          <t>html_len=93759</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
@@ -1019,7 +1019,7 @@
       <c r="I2" s="9" t="inlineStr"/>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>13:30:40</t>
+          <t>21:07:41</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>13:30:43</t>
+          <t>21:07:44</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>13:30:49</t>
+          <t>21:07:50</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>13:30:56</t>
+          <t>21:07:56</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>13:31:04</t>
+          <t>21:08:04</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>13:31:14</t>
+          <t>21:08:14</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>13:31:23</t>
+          <t>21:08:24</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>13:31:40</t>
+          <t>21:08:40</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Login with prabha.testuser@example.com / TestPrabha@9999</t>
+          <t>Login with prabha02102005@gmail.com / 123456789</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>1. Enter prabha.testuser@example.com
+          <t>1. Enter prabha02102005@gmail.com
 2. Enter password
 3. Submit</t>
         </is>
@@ -1411,16 +1411,16 @@
           <t>FAIL may mean account not registered in backend. Body snippet: Smart EV
 ASSISTANT
 P
-Prabha User
-450 Coins
+Prabha
+100 Coins
 Dashboard
 Navigation
-Stations (Chargi</t>
+Stations (Charging St</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>13:31:59</t>
+          <t>21:09:00</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>13:32:06</t>
+          <t>21:09:07</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>13:32:13</t>
+          <t>21:09:14</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>13:32:20</t>
+          <t>21:09:21</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>13:32:33</t>
+          <t>21:09:33</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       <c r="I15" s="11" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>13:32:40</t>
+          <t>21:09:40</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       <c r="I16" s="9" t="inlineStr"/>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>13:32:48</t>
+          <t>21:09:48</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>13:32:56</t>
+          <t>21:09:56</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>13:33:08</t>
+          <t>21:10:08</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>URL=http://localhost:3000/dashboard, body_len=1495</t>
+          <t>URL=http://localhost:3000/dashboard, body_len=1493</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>13:33:28</t>
+          <t>21:10:28</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       <c r="I20" s="9" t="inlineStr"/>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>13:33:44</t>
+          <t>21:10:44</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>13:33:58</t>
+          <t>21:10:58</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>13:34:13</t>
+          <t>21:11:13</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>13:34:27</t>
+          <t>21:11:27</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>13:34:41</t>
+          <t>21:11:41</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>13:34:55</t>
+          <t>21:11:55</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>13:35:03</t>
+          <t>21:12:04</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>13:35:18</t>
+          <t>21:12:18</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>13:35:32</t>
+          <t>21:12:32</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=986</t>
+          <t>URL OK=True, body_len=2194</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>13:35:40</t>
+          <t>21:12:40</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>13:35:48</t>
+          <t>21:12:49</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>13:35:59</t>
+          <t>21:12:59</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>13:36:23</t>
+          <t>21:13:23</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>13:36:31</t>
+          <t>21:13:31</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       <c r="I34" s="9" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>13:36:45</t>
+          <t>21:13:45</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       <c r="I35" s="11" t="inlineStr"/>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>13:36:54</t>
+          <t>21:13:54</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1533</t>
+          <t>URL OK=True, body_len=1599</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -2699,7 +2699,7 @@
       <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>13:37:02</t>
+          <t>21:14:02</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>13:37:16</t>
+          <t>21:14:16</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>13:37:24</t>
+          <t>21:14:24</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="I39" s="11" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>13:37:33</t>
+          <t>21:14:33</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>13:37:48</t>
+          <t>21:14:47</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>13:37:56</t>
+          <t>21:14:55</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1095</t>
+          <t>URL OK=True, body_len=1247</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -2991,7 +2991,7 @@
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>13:38:04</t>
+          <t>21:15:04</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       <c r="I43" s="11" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>13:38:18</t>
+          <t>21:15:18</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1039</t>
+          <t>URL OK=True, body_len=6540</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -3088,7 +3088,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>13:38:27</t>
+          <t>21:15:26</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       <c r="I45" s="11" t="inlineStr"/>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>13:38:41</t>
+          <t>21:15:40</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>13:38:49</t>
+          <t>21:15:49</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       <c r="I47" s="11" t="inlineStr"/>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>13:39:03</t>
+          <t>21:16:03</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>13:39:11</t>
+          <t>21:16:11</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>13:39:26</t>
+          <t>21:16:25</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>13:39:34</t>
+          <t>21:16:34</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       <c r="I51" s="11" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>13:39:42</t>
+          <t>21:16:42</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       <c r="I52" s="9" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>13:39:56</t>
+          <t>21:16:56</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=2788</t>
+          <t>URL OK=True, body_len=3029</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -3525,7 +3525,7 @@
       <c r="I53" s="11" t="inlineStr"/>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>13:40:05</t>
+          <t>21:17:05</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>13:40:19</t>
+          <t>21:17:19</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       <c r="I55" s="11" t="inlineStr"/>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>13:40:27</t>
+          <t>21:17:27</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       <c r="I56" s="9" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>13:40:41</t>
+          <t>21:17:41</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       <c r="I57" s="11" t="inlineStr"/>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>21:17:50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>21:17:50</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>13:40:56</t>
+          <t>21:17:56</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>13:41:11</t>
+          <t>21:18:11</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>13:41:19</t>
+          <t>21:18:19</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>13:41:27</t>
+          <t>21:18:27</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>13:41:41</t>
+          <t>21:18:41</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>13:42:06</t>
+          <t>21:19:07</t>
         </is>
       </c>
     </row>
@@ -4143,13 +4143,13 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>html_len=93765</t>
+          <t>html_len=93759</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr"/>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>13:30:40</t>
+          <t>21:07:41</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>13:30:43</t>
+          <t>21:07:44</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>13:30:49</t>
+          <t>21:07:50</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>13:30:56</t>
+          <t>21:07:56</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>13:31:04</t>
+          <t>21:08:04</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>13:31:14</t>
+          <t>21:08:14</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>13:31:23</t>
+          <t>21:08:24</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>13:31:40</t>
+          <t>21:08:40</t>
         </is>
       </c>
     </row>
@@ -4375,16 +4375,16 @@
           <t>FAIL may mean account not registered in backend. Body snippet: Smart EV
 ASSISTANT
 P
-Prabha User
-450 Coins
+Prabha
+100 Coins
 Dashboard
 Navigation
-Stations (Chargi</t>
+Stations (Charging St</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>13:31:59</t>
+          <t>21:09:00</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>13:32:06</t>
+          <t>21:09:07</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>13:32:13</t>
+          <t>21:09:14</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>13:32:20</t>
+          <t>21:09:21</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>13:32:33</t>
+          <t>21:09:33</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>13:32:40</t>
+          <t>21:09:40</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>13:32:48</t>
+          <t>21:09:48</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>13:32:56</t>
+          <t>21:09:56</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>13:33:08</t>
+          <t>21:10:08</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>URL=http://localhost:3000/dashboard, body_len=1495</t>
+          <t>URL=http://localhost:3000/dashboard, body_len=1493</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>13:33:28</t>
+          <t>21:10:28</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>13:33:44</t>
+          <t>21:10:44</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>13:33:58</t>
+          <t>21:10:58</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>13:34:13</t>
+          <t>21:11:13</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>13:34:27</t>
+          <t>21:11:27</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>13:34:41</t>
+          <t>21:11:41</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>13:34:55</t>
+          <t>21:11:55</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>13:35:03</t>
+          <t>21:12:04</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>13:35:18</t>
+          <t>21:12:18</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>13:35:32</t>
+          <t>21:12:32</t>
         </is>
       </c>
     </row>
@@ -4914,13 +4914,13 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=986</t>
+          <t>URL OK=True, body_len=2194</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>13:35:40</t>
+          <t>21:12:40</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>13:35:48</t>
+          <t>21:12:49</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>13:35:59</t>
+          <t>21:12:59</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>13:36:23</t>
+          <t>21:13:23</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>13:36:31</t>
+          <t>21:13:31</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>13:36:45</t>
+          <t>21:13:45</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>13:36:54</t>
+          <t>21:13:54</t>
         </is>
       </c>
     </row>
@@ -5114,13 +5114,13 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1533</t>
+          <t>URL OK=True, body_len=1599</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>13:37:02</t>
+          <t>21:14:02</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>13:37:16</t>
+          <t>21:14:16</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>13:37:24</t>
+          <t>21:14:24</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>13:37:33</t>
+          <t>21:14:33</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>13:37:48</t>
+          <t>21:14:47</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>13:37:56</t>
+          <t>21:14:55</t>
         </is>
       </c>
     </row>
@@ -5282,13 +5282,13 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1095</t>
+          <t>URL OK=True, body_len=1247</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>13:38:04</t>
+          <t>21:15:04</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>13:38:18</t>
+          <t>21:15:18</t>
         </is>
       </c>
     </row>
@@ -5338,13 +5338,13 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=1039</t>
+          <t>URL OK=True, body_len=6540</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>13:38:27</t>
+          <t>21:15:26</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       <c r="E45" s="13" t="inlineStr"/>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>13:38:41</t>
+          <t>21:15:40</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       <c r="E46" s="13" t="inlineStr"/>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>13:38:49</t>
+          <t>21:15:49</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       <c r="E47" s="13" t="inlineStr"/>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>13:39:03</t>
+          <t>21:16:03</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       <c r="E48" s="13" t="inlineStr"/>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>13:39:11</t>
+          <t>21:16:11</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       <c r="E49" s="13" t="inlineStr"/>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>13:39:26</t>
+          <t>21:16:25</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       <c r="E50" s="13" t="inlineStr"/>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>13:39:34</t>
+          <t>21:16:34</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       <c r="E51" s="13" t="inlineStr"/>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>13:39:42</t>
+          <t>21:16:42</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       <c r="E52" s="13" t="inlineStr"/>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>13:39:56</t>
+          <t>21:16:56</t>
         </is>
       </c>
     </row>
@@ -5590,13 +5590,13 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>URL OK=True, body_len=2788</t>
+          <t>URL OK=True, body_len=3029</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr"/>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>13:40:05</t>
+          <t>21:17:05</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       <c r="E54" s="13" t="inlineStr"/>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>13:40:19</t>
+          <t>21:17:19</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       <c r="E55" s="13" t="inlineStr"/>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>13:40:27</t>
+          <t>21:17:27</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       <c r="E56" s="13" t="inlineStr"/>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>13:40:41</t>
+          <t>21:17:41</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       <c r="E57" s="13" t="inlineStr"/>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>21:17:50</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       <c r="E58" s="13" t="inlineStr"/>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>13:40:50</t>
+          <t>21:17:50</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       <c r="E59" s="13" t="inlineStr"/>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>13:40:56</t>
+          <t>21:17:56</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       <c r="E60" s="13" t="inlineStr"/>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>13:41:11</t>
+          <t>21:18:11</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       <c r="E61" s="13" t="inlineStr"/>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>13:41:19</t>
+          <t>21:18:19</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>13:41:27</t>
+          <t>21:18:27</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       <c r="E63" s="13" t="inlineStr"/>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>13:41:41</t>
+          <t>21:18:41</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>13:42:06</t>
+          <t>21:19:07</t>
         </is>
       </c>
     </row>

--- a/tests/ev_test_report.xlsx
+++ b/tests/ev_test_report.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26 22:03:55</t>
+          <t>2026-06-26 22:19:48</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="I2" s="9" t="inlineStr"/>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>21:59:28</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       <c r="I15" s="11" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>21:59:28</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       <c r="I16" s="9" t="inlineStr"/>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       <c r="I19" s="11" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       <c r="I20" s="9" t="inlineStr"/>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>21:59:33</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>21:59:33</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       <c r="I34" s="9" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       <c r="I35" s="11" t="inlineStr"/>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       <c r="I39" s="11" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       <c r="I43" s="11" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       <c r="I45" s="11" t="inlineStr"/>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       <c r="I47" s="11" t="inlineStr"/>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       <c r="I51" s="11" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       <c r="I52" s="9" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       <c r="I53" s="11" t="inlineStr"/>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>21:59:41</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       <c r="I55" s="11" t="inlineStr"/>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       <c r="I56" s="9" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:35</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       <c r="I57" s="11" t="inlineStr"/>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>21:59:48</t>
+          <t>22:15:40</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>21:59:53</t>
+          <t>22:15:46</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>22:15:53</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>22:00:05</t>
+          <t>22:15:58</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>22:00:11</t>
+          <t>22:16:03</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>22:00:16</t>
+          <t>22:16:08</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>22:00:21</t>
+          <t>22:16:14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>22:00:23</t>
+          <t>22:16:16</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       <c r="I65" s="11" t="inlineStr"/>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>22:00:26</t>
+          <t>22:16:19</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       <c r="I66" s="9" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>22:00:31</t>
+          <t>22:16:24</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       <c r="I67" s="11" t="inlineStr"/>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>22:00:31</t>
+          <t>22:16:24</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>22:00:38</t>
+          <t>22:16:31</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       <c r="I69" s="11" t="inlineStr"/>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>22:00:40</t>
+          <t>22:16:33</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       <c r="I70" s="9" t="inlineStr"/>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>22:00:49</t>
+          <t>22:16:42</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       <c r="I71" s="11" t="inlineStr"/>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>22:00:54</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       <c r="I72" s="9" t="inlineStr"/>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>22:00:54</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       <c r="I73" s="11" t="inlineStr"/>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>22:01:00</t>
+          <t>22:16:52</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       <c r="I74" s="9" t="inlineStr"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>22:01:00</t>
+          <t>22:16:52</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       <c r="I75" s="11" t="inlineStr"/>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>22:01:05</t>
+          <t>22:16:58</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       <c r="I76" s="9" t="inlineStr"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>22:01:11</t>
+          <t>22:17:03</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       <c r="I77" s="11" t="inlineStr"/>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:06</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       <c r="I78" s="9" t="inlineStr"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       <c r="I79" s="11" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       <c r="I81" s="11" t="inlineStr"/>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       <c r="I82" s="9" t="inlineStr"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       <c r="I83" s="11" t="inlineStr"/>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>22:01:20</t>
+          <t>22:17:13</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>22:01:22</t>
+          <t>22:17:15</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       <c r="I85" s="11" t="inlineStr"/>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>22:01:25</t>
+          <t>22:17:18</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       <c r="I86" s="9" t="inlineStr"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>22:01:25</t>
+          <t>22:17:18</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       <c r="I87" s="11" t="inlineStr"/>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>22:01:31</t>
+          <t>22:17:24</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       <c r="I88" s="9" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>22:01:33</t>
+          <t>22:17:26</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       <c r="I89" s="11" t="inlineStr"/>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:29</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       <c r="I90" s="9" t="inlineStr"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:29</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       <c r="I91" s="11" t="inlineStr"/>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       <c r="I93" s="11" t="inlineStr"/>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       <c r="I95" s="11" t="inlineStr"/>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>22:01:42</t>
+          <t>22:17:36</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>22:01:45</t>
+          <t>22:17:38</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       <c r="I97" s="11" t="inlineStr"/>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:51</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:51</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       <c r="I99" s="11" t="inlineStr"/>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       <c r="I101" s="11" t="inlineStr"/>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       <c r="I103" s="11" t="inlineStr"/>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       <c r="I104" s="9" t="inlineStr"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       <c r="I105" s="11" t="inlineStr"/>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       <c r="I106" s="9" t="inlineStr"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:53</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       <c r="I107" s="11" t="inlineStr"/>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:53</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       <c r="I108" s="9" t="inlineStr"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>22:02:09</t>
+          <t>22:18:03</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       <c r="I109" s="11" t="inlineStr"/>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>22:02:09</t>
+          <t>22:18:03</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       <c r="I110" s="9" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       <c r="I111" s="11" t="inlineStr"/>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       <c r="I112" s="9" t="inlineStr"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       <c r="I113" s="11" t="inlineStr"/>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       <c r="I114" s="9" t="inlineStr"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="I115" s="11" t="inlineStr"/>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       <c r="I117" s="11" t="inlineStr"/>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       <c r="I119" s="11" t="inlineStr"/>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       <c r="I120" s="9" t="inlineStr"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       <c r="I121" s="11" t="inlineStr"/>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       <c r="I122" s="9" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       <c r="I123" s="11" t="inlineStr"/>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       <c r="I124" s="9" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       <c r="I125" s="11" t="inlineStr"/>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       <c r="I126" s="9" t="inlineStr"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       <c r="I127" s="11" t="inlineStr"/>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       <c r="I128" s="9" t="inlineStr"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       <c r="I129" s="11" t="inlineStr"/>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       <c r="I130" s="9" t="inlineStr"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       <c r="I131" s="11" t="inlineStr"/>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       <c r="I132" s="9" t="inlineStr"/>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       <c r="I133" s="11" t="inlineStr"/>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>22:02:23</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       <c r="I134" s="9" t="inlineStr"/>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       <c r="I135" s="11" t="inlineStr"/>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       <c r="I136" s="9" t="inlineStr"/>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       <c r="I137" s="11" t="inlineStr"/>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       <c r="I138" s="9" t="inlineStr"/>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       <c r="I139" s="11" t="inlineStr"/>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       <c r="I140" s="9" t="inlineStr"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       <c r="I141" s="11" t="inlineStr"/>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       <c r="I142" s="9" t="inlineStr"/>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="I143" s="11" t="inlineStr"/>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       <c r="I144" s="9" t="inlineStr"/>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       <c r="I145" s="11" t="inlineStr"/>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       <c r="I146" s="9" t="inlineStr"/>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       <c r="I147" s="11" t="inlineStr"/>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       <c r="I148" s="9" t="inlineStr"/>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
       <c r="I149" s="11" t="inlineStr"/>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       <c r="I150" s="9" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:22</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="I151" s="11" t="inlineStr"/>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:22</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       <c r="I152" s="9" t="inlineStr"/>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="I153" s="11" t="inlineStr"/>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       <c r="I154" s="9" t="inlineStr"/>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       <c r="I155" s="11" t="inlineStr"/>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       <c r="I156" s="9" t="inlineStr"/>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       <c r="I157" s="11" t="inlineStr"/>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       <c r="I158" s="9" t="inlineStr"/>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       <c r="I159" s="11" t="inlineStr"/>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       <c r="I160" s="9" t="inlineStr"/>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       <c r="I161" s="11" t="inlineStr"/>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       <c r="I162" s="9" t="inlineStr"/>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       <c r="I163" s="11" t="inlineStr"/>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>22:02:31</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       <c r="I164" s="9" t="inlineStr"/>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>22:02:32</t>
+          <t>22:18:25</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       <c r="I165" s="11" t="inlineStr"/>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>22:02:32</t>
+          <t>22:18:25</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       <c r="I166" s="9" t="inlineStr"/>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       <c r="I167" s="11" t="inlineStr"/>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       <c r="I168" s="9" t="inlineStr"/>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       <c r="I169" s="11" t="inlineStr"/>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>22:02:36</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       <c r="I170" s="9" t="inlineStr"/>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>22:02:36</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       <c r="I171" s="11" t="inlineStr"/>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       <c r="I172" s="9" t="inlineStr"/>
       <c r="J172" s="9" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       <c r="I173" s="11" t="inlineStr"/>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       <c r="I174" s="9" t="inlineStr"/>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9315,7 +9315,7 @@
       <c r="I175" s="11" t="inlineStr"/>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       <c r="I176" s="9" t="inlineStr"/>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       <c r="I177" s="11" t="inlineStr"/>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       <c r="I178" s="9" t="inlineStr"/>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       <c r="I179" s="11" t="inlineStr"/>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       <c r="I180" s="9" t="inlineStr"/>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
       <c r="I181" s="11" t="inlineStr"/>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       <c r="I182" s="9" t="inlineStr"/>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       <c r="I183" s="11" t="inlineStr"/>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       <c r="I184" s="9" t="inlineStr"/>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       <c r="I185" s="11" t="inlineStr"/>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       <c r="I186" s="9" t="inlineStr"/>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
       <c r="I187" s="11" t="inlineStr"/>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       <c r="I188" s="9" t="inlineStr"/>
       <c r="J188" s="9" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       <c r="I189" s="11" t="inlineStr"/>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       <c r="I190" s="9" t="inlineStr"/>
       <c r="J190" s="9" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -10083,7 +10083,7 @@
       <c r="I191" s="11" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
       <c r="I192" s="9" t="inlineStr"/>
       <c r="J192" s="9" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       <c r="I194" s="9" t="inlineStr"/>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
       <c r="I195" s="11" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       <c r="I196" s="9" t="inlineStr"/>
       <c r="J196" s="9" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       <c r="I197" s="11" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>22:02:41</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       <c r="I198" s="9" t="inlineStr"/>
       <c r="J198" s="9" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10467,7 @@
       <c r="I199" s="11" t="inlineStr"/>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       <c r="I200" s="9" t="inlineStr"/>
       <c r="J200" s="9" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       <c r="I201" s="11" t="inlineStr"/>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       <c r="I202" s="9" t="inlineStr"/>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       <c r="I203" s="11" t="inlineStr"/>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       <c r="I204" s="9" t="inlineStr"/>
       <c r="J204" s="9" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10755,7 +10755,7 @@
       <c r="I205" s="11" t="inlineStr"/>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       <c r="I206" s="9" t="inlineStr"/>
       <c r="J206" s="9" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       <c r="I207" s="11" t="inlineStr"/>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       <c r="I208" s="9" t="inlineStr"/>
       <c r="J208" s="9" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10947,7 +10947,7 @@
       <c r="I209" s="11" t="inlineStr"/>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       <c r="I210" s="9" t="inlineStr"/>
       <c r="J210" s="9" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       <c r="I211" s="11" t="inlineStr"/>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       <c r="I212" s="9" t="inlineStr"/>
       <c r="J212" s="9" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       <c r="I213" s="11" t="inlineStr"/>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       <c r="I214" s="9" t="inlineStr"/>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       <c r="I215" s="11" t="inlineStr"/>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       <c r="I216" s="9" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       <c r="I217" s="11" t="inlineStr"/>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       <c r="I218" s="9" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       <c r="I219" s="11" t="inlineStr"/>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       <c r="I220" s="9" t="inlineStr"/>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       <c r="I221" s="11" t="inlineStr"/>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       <c r="I222" s="9" t="inlineStr"/>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       <c r="I223" s="11" t="inlineStr"/>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11667,7 @@
       <c r="I224" s="9" t="inlineStr"/>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       <c r="I225" s="11" t="inlineStr"/>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       <c r="I226" s="9" t="inlineStr"/>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       <c r="I227" s="11" t="inlineStr"/>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       <c r="I228" s="9" t="inlineStr"/>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       <c r="I229" s="11" t="inlineStr"/>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>22:02:48</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       <c r="I230" s="9" t="inlineStr"/>
       <c r="J230" s="9" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       <c r="I231" s="11" t="inlineStr"/>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       <c r="I232" s="9" t="inlineStr"/>
       <c r="J232" s="9" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       <c r="I233" s="11" t="inlineStr"/>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12147,7 @@
       <c r="I234" s="9" t="inlineStr"/>
       <c r="J234" s="9" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       <c r="I235" s="11" t="inlineStr"/>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       <c r="I236" s="9" t="inlineStr"/>
       <c r="J236" s="9" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       <c r="I237" s="11" t="inlineStr"/>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       <c r="I238" s="9" t="inlineStr"/>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       <c r="I239" s="11" t="inlineStr"/>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       <c r="I240" s="9" t="inlineStr"/>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12483,7 +12483,7 @@
       <c r="I241" s="11" t="inlineStr"/>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       <c r="I242" s="9" t="inlineStr"/>
       <c r="J242" s="9" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       <c r="I243" s="11" t="inlineStr"/>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       <c r="I244" s="9" t="inlineStr"/>
       <c r="J244" s="9" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       <c r="I245" s="11" t="inlineStr"/>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       <c r="I246" s="9" t="inlineStr"/>
       <c r="J246" s="9" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       <c r="I247" s="11" t="inlineStr"/>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       <c r="I248" s="9" t="inlineStr"/>
       <c r="J248" s="9" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12867,7 +12867,7 @@
       <c r="I249" s="11" t="inlineStr"/>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12915,7 @@
       <c r="I250" s="9" t="inlineStr"/>
       <c r="J250" s="9" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       <c r="I251" s="11" t="inlineStr"/>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
       <c r="I252" s="9" t="inlineStr"/>
       <c r="J252" s="9" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       <c r="I253" s="11" t="inlineStr"/>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       <c r="I254" s="9" t="inlineStr"/>
       <c r="J254" s="9" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -13155,7 +13155,7 @@
       <c r="I255" s="11" t="inlineStr"/>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13203,7 @@
       <c r="I256" s="9" t="inlineStr"/>
       <c r="J256" s="9" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       <c r="I257" s="11" t="inlineStr"/>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>22:02:57</t>
+          <t>22:18:50</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13299,7 @@
       <c r="I258" s="9" t="inlineStr"/>
       <c r="J258" s="9" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:53</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       <c r="I259" s="11" t="inlineStr"/>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:53</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       <c r="I260" s="9" t="inlineStr"/>
       <c r="J260" s="9" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:54</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13443,7 @@
       <c r="I261" s="11" t="inlineStr"/>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:54</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       <c r="I262" s="9" t="inlineStr"/>
       <c r="J262" s="9" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       <c r="I263" s="11" t="inlineStr"/>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       <c r="I264" s="9" t="inlineStr"/>
       <c r="J264" s="9" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       <c r="I265" s="11" t="inlineStr"/>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       <c r="I266" s="9" t="inlineStr"/>
       <c r="J266" s="9" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13731,7 @@
       <c r="I267" s="11" t="inlineStr"/>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       <c r="I268" s="9" t="inlineStr"/>
       <c r="J268" s="9" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       <c r="I269" s="11" t="inlineStr"/>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
       <c r="I270" s="9" t="inlineStr"/>
       <c r="J270" s="9" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13923,7 @@
       <c r="I271" s="11" t="inlineStr"/>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -13971,7 +13971,7 @@
       <c r="I272" s="9" t="inlineStr"/>
       <c r="J272" s="9" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       <c r="I273" s="11" t="inlineStr"/>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       <c r="I274" s="9" t="inlineStr"/>
       <c r="J274" s="9" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       <c r="I275" s="11" t="inlineStr"/>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>22:03:07</t>
+          <t>22:19:01</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       <c r="I276" s="9" t="inlineStr"/>
       <c r="J276" s="9" t="inlineStr">
         <is>
-          <t>22:03:08</t>
+          <t>22:19:01</t>
         </is>
       </c>
     </row>
@@ -14211,7 +14211,7 @@
       <c r="I277" s="11" t="inlineStr"/>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       <c r="I278" s="9" t="inlineStr"/>
       <c r="J278" s="9" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -14307,7 +14307,7 @@
       <c r="I279" s="11" t="inlineStr"/>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       <c r="I280" s="9" t="inlineStr"/>
       <c r="J280" s="9" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       <c r="I281" s="11" t="inlineStr"/>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       <c r="I282" s="9" t="inlineStr"/>
       <c r="J282" s="9" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:04</t>
         </is>
       </c>
     </row>
@@ -14499,7 +14499,7 @@
       <c r="I283" s="11" t="inlineStr"/>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:04</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       <c r="I284" s="9" t="inlineStr"/>
       <c r="J284" s="9" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       <c r="I285" s="11" t="inlineStr"/>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       <c r="I286" s="9" t="inlineStr"/>
       <c r="J286" s="9" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       <c r="I287" s="11" t="inlineStr"/>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       <c r="I288" s="9" t="inlineStr"/>
       <c r="J288" s="9" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       <c r="I289" s="11" t="inlineStr"/>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       <c r="I290" s="9" t="inlineStr"/>
       <c r="J290" s="9" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14883,7 @@
       <c r="I291" s="11" t="inlineStr"/>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
       <c r="I292" s="9" t="inlineStr"/>
       <c r="J292" s="9" t="inlineStr">
         <is>
-          <t>22:03:15</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       <c r="I293" s="11" t="inlineStr"/>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       <c r="I294" s="9" t="inlineStr"/>
       <c r="J294" s="9" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       <c r="I295" s="11" t="inlineStr"/>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15123,7 @@
       <c r="I296" s="9" t="inlineStr"/>
       <c r="J296" s="9" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       <c r="I297" s="11" t="inlineStr"/>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       <c r="I298" s="9" t="inlineStr"/>
       <c r="J298" s="9" t="inlineStr">
         <is>
-          <t>22:03:17</t>
+          <t>22:19:10</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       <c r="I299" s="11" t="inlineStr"/>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>22:03:17</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       <c r="I300" s="9" t="inlineStr"/>
       <c r="J300" s="9" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       <c r="I301" s="11" t="inlineStr"/>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       <c r="I302" s="9" t="inlineStr"/>
       <c r="J302" s="9" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       <c r="I303" s="11" t="inlineStr"/>
       <c r="J303" s="11" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       <c r="I304" s="9" t="inlineStr"/>
       <c r="J304" s="9" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       <c r="I305" s="11" t="inlineStr"/>
       <c r="J305" s="11" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       <c r="I306" s="9" t="inlineStr"/>
       <c r="J306" s="9" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:14</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       <c r="I307" s="11" t="inlineStr"/>
       <c r="J307" s="11" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:14</t>
         </is>
       </c>
     </row>
@@ -15699,7 +15699,7 @@
       <c r="I308" s="9" t="inlineStr"/>
       <c r="J308" s="9" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -15747,7 +15747,7 @@
       <c r="I309" s="11" t="inlineStr"/>
       <c r="J309" s="11" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -15795,7 +15795,7 @@
       <c r="I310" s="9" t="inlineStr"/>
       <c r="J310" s="9" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       <c r="I311" s="11" t="inlineStr"/>
       <c r="J311" s="11" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       <c r="I312" s="9" t="inlineStr"/>
       <c r="J312" s="9" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       <c r="I313" s="11" t="inlineStr"/>
       <c r="J313" s="11" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -15987,7 +15987,7 @@
       <c r="I314" s="9" t="inlineStr"/>
       <c r="J314" s="9" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16035,7 @@
       <c r="I315" s="11" t="inlineStr"/>
       <c r="J315" s="11" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
       <c r="I316" s="9" t="inlineStr"/>
       <c r="J316" s="9" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:17</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       <c r="I317" s="11" t="inlineStr"/>
       <c r="J317" s="11" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:17</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       <c r="I318" s="9" t="inlineStr"/>
       <c r="J318" s="9" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       <c r="I319" s="11" t="inlineStr"/>
       <c r="J319" s="11" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       <c r="I320" s="9" t="inlineStr"/>
       <c r="J320" s="9" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       <c r="I321" s="11" t="inlineStr"/>
       <c r="J321" s="11" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16371,7 @@
       <c r="I322" s="9" t="inlineStr"/>
       <c r="J322" s="9" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
       <c r="I323" s="11" t="inlineStr"/>
       <c r="J323" s="11" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16467,7 @@
       <c r="I324" s="9" t="inlineStr"/>
       <c r="J324" s="9" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       <c r="I325" s="11" t="inlineStr"/>
       <c r="J325" s="11" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       <c r="I326" s="9" t="inlineStr"/>
       <c r="J326" s="9" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       <c r="I327" s="11" t="inlineStr"/>
       <c r="J327" s="11" t="inlineStr">
         <is>
-          <t>22:03:26</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       <c r="I328" s="9" t="inlineStr"/>
       <c r="J328" s="9" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       <c r="I329" s="11" t="inlineStr"/>
       <c r="J329" s="11" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -16755,7 +16755,7 @@
       <c r="I330" s="9" t="inlineStr"/>
       <c r="J330" s="9" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -16803,7 +16803,7 @@
       <c r="I331" s="11" t="inlineStr"/>
       <c r="J331" s="11" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -16851,7 +16851,7 @@
       <c r="I332" s="9" t="inlineStr"/>
       <c r="J332" s="9" t="inlineStr">
         <is>
-          <t>22:03:30</t>
+          <t>22:19:23</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       <c r="I333" s="11" t="inlineStr"/>
       <c r="J333" s="11" t="inlineStr">
         <is>
-          <t>22:03:30</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16947,7 @@
       <c r="I334" s="9" t="inlineStr"/>
       <c r="J334" s="9" t="inlineStr">
         <is>
-          <t>22:03:31</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       <c r="I335" s="11" t="inlineStr"/>
       <c r="J335" s="11" t="inlineStr">
         <is>
-          <t>22:03:31</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17043,7 @@
       <c r="I336" s="9" t="inlineStr"/>
       <c r="J336" s="9" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -17091,7 +17091,7 @@
       <c r="I337" s="11" t="inlineStr"/>
       <c r="J337" s="11" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -17139,7 +17139,7 @@
       <c r="I338" s="9" t="inlineStr"/>
       <c r="J338" s="9" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17187,7 @@
       <c r="I339" s="11" t="inlineStr"/>
       <c r="J339" s="11" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -17235,7 +17235,7 @@
       <c r="I340" s="9" t="inlineStr"/>
       <c r="J340" s="9" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       <c r="I341" s="11" t="inlineStr"/>
       <c r="J341" s="11" t="inlineStr">
         <is>
-          <t>22:03:33</t>
+          <t>22:19:27</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       <c r="I342" s="9" t="inlineStr"/>
       <c r="J342" s="9" t="inlineStr">
         <is>
-          <t>22:03:33</t>
+          <t>22:19:27</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
       <c r="I343" s="11" t="inlineStr"/>
       <c r="J343" s="11" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       <c r="I344" s="9" t="inlineStr"/>
       <c r="J344" s="9" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
       <c r="I345" s="11" t="inlineStr"/>
       <c r="J345" s="11" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17523,7 @@
       <c r="I346" s="9" t="inlineStr"/>
       <c r="J346" s="9" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17571,7 +17571,7 @@
       <c r="I347" s="11" t="inlineStr"/>
       <c r="J347" s="11" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       <c r="I348" s="9" t="inlineStr"/>
       <c r="J348" s="9" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -17667,7 +17667,7 @@
       <c r="I349" s="11" t="inlineStr"/>
       <c r="J349" s="11" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       <c r="I350" s="9" t="inlineStr"/>
       <c r="J350" s="9" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       <c r="I351" s="11" t="inlineStr"/>
       <c r="J351" s="11" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       <c r="I352" s="9" t="inlineStr"/>
       <c r="J352" s="9" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       <c r="I353" s="11" t="inlineStr"/>
       <c r="J353" s="11" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17907,7 +17907,7 @@
       <c r="I354" s="9" t="inlineStr"/>
       <c r="J354" s="9" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       <c r="I355" s="11" t="inlineStr"/>
       <c r="J355" s="11" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:33</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       <c r="I356" s="9" t="inlineStr"/>
       <c r="J356" s="9" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:33</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
       <c r="I357" s="11" t="inlineStr"/>
       <c r="J357" s="11" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18099,7 +18099,7 @@
       <c r="I358" s="9" t="inlineStr"/>
       <c r="J358" s="9" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       <c r="I359" s="11" t="inlineStr"/>
       <c r="J359" s="11" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18195,7 @@
       <c r="I360" s="9" t="inlineStr"/>
       <c r="J360" s="9" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18243,7 @@
       <c r="I361" s="11" t="inlineStr"/>
       <c r="J361" s="11" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       <c r="I362" s="9" t="inlineStr"/>
       <c r="J362" s="9" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18339,7 +18339,7 @@
       <c r="I363" s="11" t="inlineStr"/>
       <c r="J363" s="11" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
       <c r="I364" s="9" t="inlineStr"/>
       <c r="J364" s="9" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       <c r="I365" s="11" t="inlineStr"/>
       <c r="J365" s="11" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
       <c r="I366" s="9" t="inlineStr"/>
       <c r="J366" s="9" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18531,7 @@
       <c r="I367" s="11" t="inlineStr"/>
       <c r="J367" s="11" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       <c r="I368" s="9" t="inlineStr"/>
       <c r="J368" s="9" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       <c r="I369" s="11" t="inlineStr"/>
       <c r="J369" s="11" t="inlineStr">
         <is>
-          <t>22:03:43</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       <c r="I370" s="9" t="inlineStr"/>
       <c r="J370" s="9" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       <c r="I371" s="11" t="inlineStr"/>
       <c r="J371" s="11" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
       <c r="I372" s="9" t="inlineStr"/>
       <c r="J372" s="9" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       <c r="I373" s="11" t="inlineStr"/>
       <c r="J373" s="11" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       <c r="I374" s="9" t="inlineStr"/>
       <c r="J374" s="9" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18915,7 @@
       <c r="I375" s="11" t="inlineStr"/>
       <c r="J375" s="11" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -18963,7 +18963,7 @@
       <c r="I376" s="9" t="inlineStr"/>
       <c r="J376" s="9" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       <c r="I377" s="11" t="inlineStr"/>
       <c r="J377" s="11" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       <c r="I378" s="9" t="inlineStr"/>
       <c r="J378" s="9" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       <c r="I379" s="11" t="inlineStr"/>
       <c r="J379" s="11" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       <c r="I380" s="9" t="inlineStr"/>
       <c r="J380" s="9" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19203,7 +19203,7 @@
       <c r="I381" s="11" t="inlineStr"/>
       <c r="J381" s="11" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19251,7 @@
       <c r="I382" s="9" t="inlineStr"/>
       <c r="J382" s="9" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       <c r="I383" s="11" t="inlineStr"/>
       <c r="J383" s="11" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19347,7 @@
       <c r="I384" s="9" t="inlineStr"/>
       <c r="J384" s="9" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -19395,7 +19395,7 @@
       <c r="I385" s="11" t="inlineStr"/>
       <c r="J385" s="11" t="inlineStr">
         <is>
-          <t>22:03:48</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -19443,7 +19443,7 @@
       <c r="I386" s="9" t="inlineStr"/>
       <c r="J386" s="9" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       <c r="I387" s="11" t="inlineStr"/>
       <c r="J387" s="11" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       <c r="I388" s="9" t="inlineStr"/>
       <c r="J388" s="9" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -19587,7 +19587,7 @@
       <c r="I389" s="11" t="inlineStr"/>
       <c r="J389" s="11" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       <c r="I390" s="9" t="inlineStr"/>
       <c r="J390" s="9" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       <c r="I391" s="11" t="inlineStr"/>
       <c r="J391" s="11" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19732,7 @@
       <c r="I392" s="9" t="inlineStr"/>
       <c r="J392" s="9" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       <c r="I393" s="11" t="inlineStr"/>
       <c r="J393" s="11" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19828,7 @@
       <c r="I394" s="9" t="inlineStr"/>
       <c r="J394" s="9" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       <c r="I395" s="11" t="inlineStr"/>
       <c r="J395" s="11" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       <c r="I396" s="9" t="inlineStr"/>
       <c r="J396" s="9" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -19973,7 +19973,7 @@
       <c r="I397" s="11" t="inlineStr"/>
       <c r="J397" s="11" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -20021,7 +20021,7 @@
       <c r="I398" s="9" t="inlineStr"/>
       <c r="J398" s="9" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -20069,7 +20069,7 @@
       <c r="I399" s="11" t="inlineStr"/>
       <c r="J399" s="11" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       <c r="I400" s="9" t="inlineStr"/>
       <c r="J400" s="9" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
       <c r="I401" s="11" t="inlineStr"/>
       <c r="J401" s="11" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20248,7 @@
       <c r="E2" s="13" t="inlineStr"/>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20276,7 @@
       <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -20304,7 +20304,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20332,7 @@
       <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>21:59:26</t>
+          <t>22:15:18</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20360,7 @@
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20416,7 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20444,7 +20444,7 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20472,7 +20472,7 @@
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20500,7 +20500,7 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:19</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>21:59:27</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>21:59:28</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20612,7 @@
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>21:59:28</t>
+          <t>22:15:20</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20696,7 @@
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:23</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20780,7 +20780,7 @@
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>21:59:31</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20836,7 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20864,7 +20864,7 @@
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:24</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20892,7 @@
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -20920,7 +20920,7 @@
       <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -20976,7 +20976,7 @@
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>21:59:32</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -21060,7 +21060,7 @@
       <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>21:59:33</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>21:59:33</t>
+          <t>22:15:25</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
       <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21144,7 @@
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21200,7 @@
       <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>21:59:36</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21228,7 +21228,7 @@
       <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21256,7 +21256,7 @@
       <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:29</t>
         </is>
       </c>
     </row>
@@ -21312,7 +21312,7 @@
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
       <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>21:59:37</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21452,7 @@
       <c r="E45" s="13" t="inlineStr"/>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21480,7 +21480,7 @@
       <c r="E46" s="13" t="inlineStr"/>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       <c r="E47" s="13" t="inlineStr"/>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:30</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       <c r="E48" s="13" t="inlineStr"/>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -21564,7 +21564,7 @@
       <c r="E49" s="13" t="inlineStr"/>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -21592,7 +21592,7 @@
       <c r="E50" s="13" t="inlineStr"/>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       <c r="E51" s="13" t="inlineStr"/>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -21648,7 +21648,7 @@
       <c r="E52" s="13" t="inlineStr"/>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>21:59:38</t>
+          <t>22:15:31</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21676,7 @@
       <c r="E53" s="13" t="inlineStr"/>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>21:59:41</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -21704,7 +21704,7 @@
       <c r="E54" s="13" t="inlineStr"/>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -21732,7 +21732,7 @@
       <c r="E55" s="13" t="inlineStr"/>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:34</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       <c r="E56" s="13" t="inlineStr"/>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>21:59:42</t>
+          <t>22:15:35</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21788,7 @@
       <c r="E57" s="13" t="inlineStr"/>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>21:59:48</t>
+          <t>22:15:40</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21816,7 @@
       <c r="E58" s="13" t="inlineStr"/>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>21:59:53</t>
+          <t>22:15:46</t>
         </is>
       </c>
     </row>
@@ -21844,7 +21844,7 @@
       <c r="E59" s="13" t="inlineStr"/>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>22:15:53</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       <c r="E60" s="13" t="inlineStr"/>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>22:00:05</t>
+          <t>22:15:58</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       <c r="E61" s="13" t="inlineStr"/>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>22:00:11</t>
+          <t>22:16:03</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>22:00:16</t>
+          <t>22:16:08</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       <c r="E63" s="13" t="inlineStr"/>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>22:00:21</t>
+          <t>22:16:14</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       <c r="E64" s="13" t="inlineStr"/>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>22:00:23</t>
+          <t>22:16:16</t>
         </is>
       </c>
     </row>
@@ -22012,7 +22012,7 @@
       <c r="E65" s="13" t="inlineStr"/>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>22:00:26</t>
+          <t>22:16:19</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
       <c r="E66" s="13" t="inlineStr"/>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>22:00:31</t>
+          <t>22:16:24</t>
         </is>
       </c>
     </row>
@@ -22068,7 +22068,7 @@
       <c r="E67" s="13" t="inlineStr"/>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>22:00:31</t>
+          <t>22:16:24</t>
         </is>
       </c>
     </row>
@@ -22096,7 +22096,7 @@
       <c r="E68" s="13" t="inlineStr"/>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>22:00:38</t>
+          <t>22:16:31</t>
         </is>
       </c>
     </row>
@@ -22124,7 +22124,7 @@
       <c r="E69" s="13" t="inlineStr"/>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>22:00:40</t>
+          <t>22:16:33</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       <c r="E70" s="13" t="inlineStr"/>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>22:00:49</t>
+          <t>22:16:42</t>
         </is>
       </c>
     </row>
@@ -22180,7 +22180,7 @@
       <c r="E71" s="13" t="inlineStr"/>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>22:00:54</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22208,7 @@
       <c r="E72" s="13" t="inlineStr"/>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>22:00:54</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -22236,7 +22236,7 @@
       <c r="E73" s="13" t="inlineStr"/>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>22:01:00</t>
+          <t>22:16:52</t>
         </is>
       </c>
     </row>
@@ -22264,7 +22264,7 @@
       <c r="E74" s="13" t="inlineStr"/>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>22:01:00</t>
+          <t>22:16:52</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       <c r="E75" s="13" t="inlineStr"/>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>22:01:05</t>
+          <t>22:16:58</t>
         </is>
       </c>
     </row>
@@ -22320,7 +22320,7 @@
       <c r="E76" s="13" t="inlineStr"/>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>22:01:11</t>
+          <t>22:17:03</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22348,7 @@
       <c r="E77" s="13" t="inlineStr"/>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:06</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22376,7 @@
       <c r="E78" s="13" t="inlineStr"/>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -22404,7 +22404,7 @@
       <c r="E79" s="13" t="inlineStr"/>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       <c r="E80" s="13" t="inlineStr"/>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -22460,7 +22460,7 @@
       <c r="E81" s="13" t="inlineStr"/>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -22488,7 +22488,7 @@
       <c r="E82" s="13" t="inlineStr"/>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>22:01:14</t>
+          <t>22:17:07</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
       <c r="E83" s="13" t="inlineStr"/>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>22:01:20</t>
+          <t>22:17:13</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       <c r="E84" s="13" t="inlineStr"/>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>22:01:22</t>
+          <t>22:17:15</t>
         </is>
       </c>
     </row>
@@ -22572,7 +22572,7 @@
       <c r="E85" s="13" t="inlineStr"/>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>22:01:25</t>
+          <t>22:17:18</t>
         </is>
       </c>
     </row>
@@ -22600,7 +22600,7 @@
       <c r="E86" s="13" t="inlineStr"/>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>22:01:25</t>
+          <t>22:17:18</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       <c r="E87" s="13" t="inlineStr"/>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>22:01:31</t>
+          <t>22:17:24</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       <c r="E88" s="13" t="inlineStr"/>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>22:01:33</t>
+          <t>22:17:26</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       <c r="E89" s="13" t="inlineStr"/>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:29</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22712,7 @@
       <c r="E90" s="13" t="inlineStr"/>
       <c r="F90" s="13" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:29</t>
         </is>
       </c>
     </row>
@@ -22740,7 +22740,7 @@
       <c r="E91" s="13" t="inlineStr"/>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>22:01:36</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       <c r="E92" s="13" t="inlineStr"/>
       <c r="F92" s="13" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
       <c r="E93" s="13" t="inlineStr"/>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -22824,7 +22824,7 @@
       <c r="E94" s="13" t="inlineStr"/>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>22:01:37</t>
+          <t>22:17:30</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       <c r="E95" s="13" t="inlineStr"/>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>22:01:42</t>
+          <t>22:17:36</t>
         </is>
       </c>
     </row>
@@ -22880,7 +22880,7 @@
       <c r="E96" s="13" t="inlineStr"/>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>22:01:45</t>
+          <t>22:17:38</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       <c r="E97" s="13" t="inlineStr"/>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:51</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       <c r="E98" s="13" t="inlineStr"/>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:51</t>
         </is>
       </c>
     </row>
@@ -22964,7 +22964,7 @@
       <c r="E99" s="13" t="inlineStr"/>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -22992,7 +22992,7 @@
       <c r="E100" s="13" t="inlineStr"/>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23020,7 @@
       <c r="E101" s="13" t="inlineStr"/>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       <c r="E102" s="13" t="inlineStr"/>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>22:01:58</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23076,7 @@
       <c r="E103" s="13" t="inlineStr"/>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23104,7 +23104,7 @@
       <c r="E104" s="13" t="inlineStr"/>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23132,7 @@
       <c r="E105" s="13" t="inlineStr"/>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:52</t>
         </is>
       </c>
     </row>
@@ -23160,7 +23160,7 @@
       <c r="E106" s="13" t="inlineStr"/>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:53</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       <c r="E107" s="13" t="inlineStr"/>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>22:01:59</t>
+          <t>22:17:53</t>
         </is>
       </c>
     </row>
@@ -23216,7 +23216,7 @@
       <c r="E108" s="13" t="inlineStr"/>
       <c r="F108" s="13" t="inlineStr">
         <is>
-          <t>22:02:09</t>
+          <t>22:18:03</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       <c r="E109" s="13" t="inlineStr"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>22:02:09</t>
+          <t>22:18:03</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       <c r="E110" s="13" t="inlineStr"/>
       <c r="F110" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -23300,7 +23300,7 @@
       <c r="E111" s="13" t="inlineStr"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23328,7 @@
       <c r="E112" s="13" t="inlineStr"/>
       <c r="F112" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:13</t>
         </is>
       </c>
     </row>
@@ -23356,7 +23356,7 @@
       <c r="E113" s="13" t="inlineStr"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       <c r="E114" s="13" t="inlineStr"/>
       <c r="F114" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       <c r="E115" s="13" t="inlineStr"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       <c r="E116" s="13" t="inlineStr"/>
       <c r="F116" s="13" t="inlineStr">
         <is>
-          <t>22:02:20</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23468,7 +23468,7 @@
       <c r="E117" s="13" t="inlineStr"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23496,7 +23496,7 @@
       <c r="E118" s="13" t="inlineStr"/>
       <c r="F118" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
       <c r="E119" s="13" t="inlineStr"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23552,7 +23552,7 @@
       <c r="E120" s="13" t="inlineStr"/>
       <c r="F120" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       <c r="E121" s="13" t="inlineStr"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:14</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       <c r="E122" s="13" t="inlineStr"/>
       <c r="F122" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23636,7 @@
       <c r="E123" s="13" t="inlineStr"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       <c r="E124" s="13" t="inlineStr"/>
       <c r="F124" s="13" t="inlineStr">
         <is>
-          <t>22:02:21</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       <c r="E125" s="13" t="inlineStr"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23720,7 +23720,7 @@
       <c r="E126" s="13" t="inlineStr"/>
       <c r="F126" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23748,7 @@
       <c r="E127" s="13" t="inlineStr"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23776,7 @@
       <c r="E128" s="13" t="inlineStr"/>
       <c r="F128" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
       <c r="E129" s="13" t="inlineStr"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:15</t>
         </is>
       </c>
     </row>
@@ -23832,7 +23832,7 @@
       <c r="E130" s="13" t="inlineStr"/>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       <c r="E131" s="13" t="inlineStr"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       <c r="E132" s="13" t="inlineStr"/>
       <c r="F132" s="13" t="inlineStr">
         <is>
-          <t>22:02:22</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       <c r="E133" s="13" t="inlineStr"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>22:02:23</t>
+          <t>22:18:16</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       <c r="E134" s="13" t="inlineStr"/>
       <c r="F134" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -23972,7 +23972,7 @@
       <c r="E135" s="13" t="inlineStr"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -24000,7 +24000,7 @@
       <c r="E136" s="13" t="inlineStr"/>
       <c r="F136" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -24028,7 +24028,7 @@
       <c r="E137" s="13" t="inlineStr"/>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:19</t>
         </is>
       </c>
     </row>
@@ -24056,7 +24056,7 @@
       <c r="E138" s="13" t="inlineStr"/>
       <c r="F138" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       <c r="E139" s="13" t="inlineStr"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>22:02:26</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24112,7 +24112,7 @@
       <c r="E140" s="13" t="inlineStr"/>
       <c r="F140" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
       <c r="E141" s="13" t="inlineStr"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24168,7 @@
       <c r="E142" s="13" t="inlineStr"/>
       <c r="F142" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24196,7 +24196,7 @@
       <c r="E143" s="13" t="inlineStr"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:20</t>
         </is>
       </c>
     </row>
@@ -24224,7 +24224,7 @@
       <c r="E144" s="13" t="inlineStr"/>
       <c r="F144" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24252,7 @@
       <c r="E145" s="13" t="inlineStr"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       <c r="E146" s="13" t="inlineStr"/>
       <c r="F146" s="13" t="inlineStr">
         <is>
-          <t>22:02:27</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24308,7 +24308,7 @@
       <c r="E147" s="13" t="inlineStr"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24336,7 +24336,7 @@
       <c r="E148" s="13" t="inlineStr"/>
       <c r="F148" s="13" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       <c r="E149" s="13" t="inlineStr"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>22:02:28</t>
+          <t>22:18:21</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24392,7 @@
       <c r="E150" s="13" t="inlineStr"/>
       <c r="F150" s="13" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:22</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       <c r="E151" s="13" t="inlineStr"/>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:22</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       <c r="E152" s="13" t="inlineStr"/>
       <c r="F152" s="13" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24476,7 @@
       <c r="E153" s="13" t="inlineStr"/>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24504,7 +24504,7 @@
       <c r="E154" s="13" t="inlineStr"/>
       <c r="F154" s="13" t="inlineStr">
         <is>
-          <t>22:02:29</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24532,7 @@
       <c r="E155" s="13" t="inlineStr"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24560,7 +24560,7 @@
       <c r="E156" s="13" t="inlineStr"/>
       <c r="F156" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       <c r="E157" s="13" t="inlineStr"/>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
       <c r="E158" s="13" t="inlineStr"/>
       <c r="F158" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24644,7 +24644,7 @@
       <c r="E159" s="13" t="inlineStr"/>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:23</t>
         </is>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
       <c r="E160" s="13" t="inlineStr"/>
       <c r="F160" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -24700,7 +24700,7 @@
       <c r="E161" s="13" t="inlineStr"/>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
       <c r="E162" s="13" t="inlineStr"/>
       <c r="F162" s="13" t="inlineStr">
         <is>
-          <t>22:02:30</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
       <c r="E163" s="13" t="inlineStr"/>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>22:02:31</t>
+          <t>22:18:24</t>
         </is>
       </c>
     </row>
@@ -24784,7 +24784,7 @@
       <c r="E164" s="13" t="inlineStr"/>
       <c r="F164" s="13" t="inlineStr">
         <is>
-          <t>22:02:32</t>
+          <t>22:18:25</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       <c r="E165" s="13" t="inlineStr"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>22:02:32</t>
+          <t>22:18:25</t>
         </is>
       </c>
     </row>
@@ -24840,7 +24840,7 @@
       <c r="E166" s="13" t="inlineStr"/>
       <c r="F166" s="13" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -24868,7 +24868,7 @@
       <c r="E167" s="13" t="inlineStr"/>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       <c r="E168" s="13" t="inlineStr"/>
       <c r="F168" s="13" t="inlineStr">
         <is>
-          <t>22:02:35</t>
+          <t>22:18:28</t>
         </is>
       </c>
     </row>
@@ -24924,7 +24924,7 @@
       <c r="E169" s="13" t="inlineStr"/>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>22:02:36</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -24952,7 +24952,7 @@
       <c r="E170" s="13" t="inlineStr"/>
       <c r="F170" s="13" t="inlineStr">
         <is>
-          <t>22:02:36</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -24980,7 +24980,7 @@
       <c r="E171" s="13" t="inlineStr"/>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25008,7 +25008,7 @@
       <c r="E172" s="13" t="inlineStr"/>
       <c r="F172" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25036,7 +25036,7 @@
       <c r="E173" s="13" t="inlineStr"/>
       <c r="F173" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25064,7 +25064,7 @@
       <c r="E174" s="13" t="inlineStr"/>
       <c r="F174" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25092,7 +25092,7 @@
       <c r="E175" s="13" t="inlineStr"/>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25120,7 @@
       <c r="E176" s="13" t="inlineStr"/>
       <c r="F176" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:30</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25148,7 @@
       <c r="E177" s="13" t="inlineStr"/>
       <c r="F177" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       <c r="E178" s="13" t="inlineStr"/>
       <c r="F178" s="13" t="inlineStr">
         <is>
-          <t>22:02:37</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25204,7 @@
       <c r="E179" s="13" t="inlineStr"/>
       <c r="F179" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       <c r="E180" s="13" t="inlineStr"/>
       <c r="F180" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25260,7 +25260,7 @@
       <c r="E181" s="13" t="inlineStr"/>
       <c r="F181" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       <c r="E182" s="13" t="inlineStr"/>
       <c r="F182" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25316,7 @@
       <c r="E183" s="13" t="inlineStr"/>
       <c r="F183" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25344,7 +25344,7 @@
       <c r="E184" s="13" t="inlineStr"/>
       <c r="F184" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:31</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       <c r="E185" s="13" t="inlineStr"/>
       <c r="F185" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25400,7 +25400,7 @@
       <c r="E186" s="13" t="inlineStr"/>
       <c r="F186" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       <c r="E187" s="13" t="inlineStr"/>
       <c r="F187" s="13" t="inlineStr">
         <is>
-          <t>22:02:38</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       <c r="E188" s="13" t="inlineStr"/>
       <c r="F188" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25484,7 @@
       <c r="E189" s="13" t="inlineStr"/>
       <c r="F189" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       <c r="E190" s="13" t="inlineStr"/>
       <c r="F190" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
       <c r="E191" s="13" t="inlineStr"/>
       <c r="F191" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25568,7 +25568,7 @@
       <c r="E192" s="13" t="inlineStr"/>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25596,7 +25596,7 @@
       <c r="E193" s="13" t="inlineStr"/>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>22:02:39</t>
+          <t>22:18:32</t>
         </is>
       </c>
     </row>
@@ -25624,7 +25624,7 @@
       <c r="E194" s="13" t="inlineStr"/>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -25652,7 +25652,7 @@
       <c r="E195" s="13" t="inlineStr"/>
       <c r="F195" s="13" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -25680,7 +25680,7 @@
       <c r="E196" s="13" t="inlineStr"/>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>22:02:40</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -25708,7 +25708,7 @@
       <c r="E197" s="13" t="inlineStr"/>
       <c r="F197" s="13" t="inlineStr">
         <is>
-          <t>22:02:41</t>
+          <t>22:18:34</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       <c r="E198" s="13" t="inlineStr"/>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       <c r="E199" s="13" t="inlineStr"/>
       <c r="F199" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
       <c r="E200" s="13" t="inlineStr"/>
       <c r="F200" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -25820,7 +25820,7 @@
       <c r="E201" s="13" t="inlineStr"/>
       <c r="F201" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:37</t>
         </is>
       </c>
     </row>
@@ -25848,7 +25848,7 @@
       <c r="E202" s="13" t="inlineStr"/>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -25876,7 +25876,7 @@
       <c r="E203" s="13" t="inlineStr"/>
       <c r="F203" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25904,7 @@
       <c r="E204" s="13" t="inlineStr"/>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>22:02:44</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       <c r="E205" s="13" t="inlineStr"/>
       <c r="F205" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       <c r="E206" s="13" t="inlineStr"/>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       <c r="E207" s="13" t="inlineStr"/>
       <c r="F207" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -26016,7 +26016,7 @@
       <c r="E208" s="13" t="inlineStr"/>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       <c r="E209" s="13" t="inlineStr"/>
       <c r="F209" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:38</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26072,7 @@
       <c r="E210" s="13" t="inlineStr"/>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26100,7 +26100,7 @@
       <c r="E211" s="13" t="inlineStr"/>
       <c r="F211" s="13" t="inlineStr">
         <is>
-          <t>22:02:45</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26128,7 +26128,7 @@
       <c r="E212" s="13" t="inlineStr"/>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26156,7 +26156,7 @@
       <c r="E213" s="13" t="inlineStr"/>
       <c r="F213" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       <c r="E214" s="13" t="inlineStr"/>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26212,7 +26212,7 @@
       <c r="E215" s="13" t="inlineStr"/>
       <c r="F215" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       <c r="E216" s="13" t="inlineStr"/>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26268,7 +26268,7 @@
       <c r="E217" s="13" t="inlineStr"/>
       <c r="F217" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:39</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       <c r="E218" s="13" t="inlineStr"/>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26324,7 +26324,7 @@
       <c r="E219" s="13" t="inlineStr"/>
       <c r="F219" s="13" t="inlineStr">
         <is>
-          <t>22:02:46</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26352,7 +26352,7 @@
       <c r="E220" s="13" t="inlineStr"/>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26380,7 @@
       <c r="E221" s="13" t="inlineStr"/>
       <c r="F221" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26408,7 @@
       <c r="E222" s="13" t="inlineStr"/>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26436,7 +26436,7 @@
       <c r="E223" s="13" t="inlineStr"/>
       <c r="F223" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26464,7 @@
       <c r="E224" s="13" t="inlineStr"/>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26492,7 +26492,7 @@
       <c r="E225" s="13" t="inlineStr"/>
       <c r="F225" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26520,7 @@
       <c r="E226" s="13" t="inlineStr"/>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:40</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       <c r="E227" s="13" t="inlineStr"/>
       <c r="F227" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
       <c r="E228" s="13" t="inlineStr"/>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>22:02:47</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -26604,7 +26604,7 @@
       <c r="E229" s="13" t="inlineStr"/>
       <c r="F229" s="13" t="inlineStr">
         <is>
-          <t>22:02:48</t>
+          <t>22:18:41</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
       <c r="E230" s="13" t="inlineStr"/>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26660,7 @@
       <c r="E231" s="13" t="inlineStr"/>
       <c r="F231" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       <c r="E232" s="13" t="inlineStr"/>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       <c r="E233" s="13" t="inlineStr"/>
       <c r="F233" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26744,7 @@
       <c r="E234" s="13" t="inlineStr"/>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:44</t>
         </is>
       </c>
     </row>
@@ -26772,7 +26772,7 @@
       <c r="E235" s="13" t="inlineStr"/>
       <c r="F235" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26800,7 +26800,7 @@
       <c r="E236" s="13" t="inlineStr"/>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>22:02:51</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26828,7 +26828,7 @@
       <c r="E237" s="13" t="inlineStr"/>
       <c r="F237" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26856,7 +26856,7 @@
       <c r="E238" s="13" t="inlineStr"/>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26884,7 +26884,7 @@
       <c r="E239" s="13" t="inlineStr"/>
       <c r="F239" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26912,7 +26912,7 @@
       <c r="E240" s="13" t="inlineStr"/>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
       <c r="E241" s="13" t="inlineStr"/>
       <c r="F241" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26968,7 +26968,7 @@
       <c r="E242" s="13" t="inlineStr"/>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -26996,7 +26996,7 @@
       <c r="E243" s="13" t="inlineStr"/>
       <c r="F243" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:45</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       <c r="E244" s="13" t="inlineStr"/>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>22:02:52</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27052,7 +27052,7 @@
       <c r="E245" s="13" t="inlineStr"/>
       <c r="F245" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27080,7 +27080,7 @@
       <c r="E246" s="13" t="inlineStr"/>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27108,7 +27108,7 @@
       <c r="E247" s="13" t="inlineStr"/>
       <c r="F247" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       <c r="E248" s="13" t="inlineStr"/>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27164,7 @@
       <c r="E249" s="13" t="inlineStr"/>
       <c r="F249" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27192,7 +27192,7 @@
       <c r="E250" s="13" t="inlineStr"/>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27220,7 @@
       <c r="E251" s="13" t="inlineStr"/>
       <c r="F251" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:46</t>
         </is>
       </c>
     </row>
@@ -27248,7 +27248,7 @@
       <c r="E252" s="13" t="inlineStr"/>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -27276,7 +27276,7 @@
       <c r="E253" s="13" t="inlineStr"/>
       <c r="F253" s="13" t="inlineStr">
         <is>
-          <t>22:02:53</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -27304,7 +27304,7 @@
       <c r="E254" s="13" t="inlineStr"/>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -27332,7 +27332,7 @@
       <c r="E255" s="13" t="inlineStr"/>
       <c r="F255" s="13" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -27360,7 +27360,7 @@
       <c r="E256" s="13" t="inlineStr"/>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>22:02:54</t>
+          <t>22:18:47</t>
         </is>
       </c>
     </row>
@@ -27388,7 +27388,7 @@
       <c r="E257" s="13" t="inlineStr"/>
       <c r="F257" s="13" t="inlineStr">
         <is>
-          <t>22:02:57</t>
+          <t>22:18:50</t>
         </is>
       </c>
     </row>
@@ -27416,7 +27416,7 @@
       <c r="E258" s="13" t="inlineStr"/>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:53</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       <c r="E259" s="13" t="inlineStr"/>
       <c r="F259" s="13" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:53</t>
         </is>
       </c>
     </row>
@@ -27472,7 +27472,7 @@
       <c r="E260" s="13" t="inlineStr"/>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:54</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       <c r="E261" s="13" t="inlineStr"/>
       <c r="F261" s="13" t="inlineStr">
         <is>
-          <t>22:03:00</t>
+          <t>22:18:54</t>
         </is>
       </c>
     </row>
@@ -27528,7 +27528,7 @@
       <c r="E262" s="13" t="inlineStr"/>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -27556,7 +27556,7 @@
       <c r="E263" s="13" t="inlineStr"/>
       <c r="F263" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -27584,7 +27584,7 @@
       <c r="E264" s="13" t="inlineStr"/>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -27612,7 +27612,7 @@
       <c r="E265" s="13" t="inlineStr"/>
       <c r="F265" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27640,7 @@
       <c r="E266" s="13" t="inlineStr"/>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:56</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       <c r="E267" s="13" t="inlineStr"/>
       <c r="F267" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27696,7 +27696,7 @@
       <c r="E268" s="13" t="inlineStr"/>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27724,7 +27724,7 @@
       <c r="E269" s="13" t="inlineStr"/>
       <c r="F269" s="13" t="inlineStr">
         <is>
-          <t>22:03:03</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27752,7 +27752,7 @@
       <c r="E270" s="13" t="inlineStr"/>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27780,7 @@
       <c r="E271" s="13" t="inlineStr"/>
       <c r="F271" s="13" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27808,7 +27808,7 @@
       <c r="E272" s="13" t="inlineStr"/>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27836,7 @@
       <c r="E273" s="13" t="inlineStr"/>
       <c r="F273" s="13" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27864,7 +27864,7 @@
       <c r="E274" s="13" t="inlineStr"/>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>22:03:04</t>
+          <t>22:18:57</t>
         </is>
       </c>
     </row>
@@ -27892,7 +27892,7 @@
       <c r="E275" s="13" t="inlineStr"/>
       <c r="F275" s="13" t="inlineStr">
         <is>
-          <t>22:03:07</t>
+          <t>22:19:01</t>
         </is>
       </c>
     </row>
@@ -27920,7 +27920,7 @@
       <c r="E276" s="13" t="inlineStr"/>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>22:03:08</t>
+          <t>22:19:01</t>
         </is>
       </c>
     </row>
@@ -27948,7 +27948,7 @@
       <c r="E277" s="13" t="inlineStr"/>
       <c r="F277" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -27976,7 +27976,7 @@
       <c r="E278" s="13" t="inlineStr"/>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       <c r="E279" s="13" t="inlineStr"/>
       <c r="F279" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -28032,7 +28032,7 @@
       <c r="E280" s="13" t="inlineStr"/>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -28060,7 +28060,7 @@
       <c r="E281" s="13" t="inlineStr"/>
       <c r="F281" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:03</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28088,7 @@
       <c r="E282" s="13" t="inlineStr"/>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:04</t>
         </is>
       </c>
     </row>
@@ -28116,7 +28116,7 @@
       <c r="E283" s="13" t="inlineStr"/>
       <c r="F283" s="13" t="inlineStr">
         <is>
-          <t>22:03:10</t>
+          <t>22:19:04</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28144,7 @@
       <c r="E284" s="13" t="inlineStr"/>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
       <c r="E285" s="13" t="inlineStr"/>
       <c r="F285" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       <c r="E286" s="13" t="inlineStr"/>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
       <c r="E287" s="13" t="inlineStr"/>
       <c r="F287" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28256,7 +28256,7 @@
       <c r="E288" s="13" t="inlineStr"/>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28284,7 @@
       <c r="E289" s="13" t="inlineStr"/>
       <c r="F289" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:07</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28312,7 @@
       <c r="E290" s="13" t="inlineStr"/>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -28340,7 +28340,7 @@
       <c r="E291" s="13" t="inlineStr"/>
       <c r="F291" s="13" t="inlineStr">
         <is>
-          <t>22:03:14</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       <c r="E292" s="13" t="inlineStr"/>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>22:03:15</t>
+          <t>22:19:08</t>
         </is>
       </c>
     </row>
@@ -28396,7 +28396,7 @@
       <c r="E293" s="13" t="inlineStr"/>
       <c r="F293" s="13" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -28424,7 +28424,7 @@
       <c r="E294" s="13" t="inlineStr"/>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -28452,7 +28452,7 @@
       <c r="E295" s="13" t="inlineStr"/>
       <c r="F295" s="13" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28480,7 @@
       <c r="E296" s="13" t="inlineStr"/>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -28508,7 +28508,7 @@
       <c r="E297" s="13" t="inlineStr"/>
       <c r="F297" s="13" t="inlineStr">
         <is>
-          <t>22:03:16</t>
+          <t>22:19:09</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       <c r="E298" s="13" t="inlineStr"/>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>22:03:17</t>
+          <t>22:19:10</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
       <c r="E299" s="13" t="inlineStr"/>
       <c r="F299" s="13" t="inlineStr">
         <is>
-          <t>22:03:17</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28592,7 +28592,7 @@
       <c r="E300" s="13" t="inlineStr"/>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28620,7 +28620,7 @@
       <c r="E301" s="13" t="inlineStr"/>
       <c r="F301" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28648,7 +28648,7 @@
       <c r="E302" s="13" t="inlineStr"/>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       <c r="E303" s="13" t="inlineStr"/>
       <c r="F303" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28704,7 +28704,7 @@
       <c r="E304" s="13" t="inlineStr"/>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28732,7 +28732,7 @@
       <c r="E305" s="13" t="inlineStr"/>
       <c r="F305" s="13" t="inlineStr">
         <is>
-          <t>22:03:18</t>
+          <t>22:19:11</t>
         </is>
       </c>
     </row>
@@ -28760,7 +28760,7 @@
       <c r="E306" s="13" t="inlineStr"/>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:14</t>
         </is>
       </c>
     </row>
@@ -28788,7 +28788,7 @@
       <c r="E307" s="13" t="inlineStr"/>
       <c r="F307" s="13" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:14</t>
         </is>
       </c>
     </row>
@@ -28816,7 +28816,7 @@
       <c r="E308" s="13" t="inlineStr"/>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>22:03:21</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28844,7 @@
       <c r="E309" s="13" t="inlineStr"/>
       <c r="F309" s="13" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -28872,7 +28872,7 @@
       <c r="E310" s="13" t="inlineStr"/>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       <c r="E311" s="13" t="inlineStr"/>
       <c r="F311" s="13" t="inlineStr">
         <is>
-          <t>22:03:22</t>
+          <t>22:19:15</t>
         </is>
       </c>
     </row>
@@ -28928,7 +28928,7 @@
       <c r="E312" s="13" t="inlineStr"/>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -28956,7 +28956,7 @@
       <c r="E313" s="13" t="inlineStr"/>
       <c r="F313" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -28984,7 +28984,7 @@
       <c r="E314" s="13" t="inlineStr"/>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -29012,7 +29012,7 @@
       <c r="E315" s="13" t="inlineStr"/>
       <c r="F315" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:16</t>
         </is>
       </c>
     </row>
@@ -29040,7 +29040,7 @@
       <c r="E316" s="13" t="inlineStr"/>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:17</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29068,7 @@
       <c r="E317" s="13" t="inlineStr"/>
       <c r="F317" s="13" t="inlineStr">
         <is>
-          <t>22:03:23</t>
+          <t>22:19:17</t>
         </is>
       </c>
     </row>
@@ -29096,7 +29096,7 @@
       <c r="E318" s="13" t="inlineStr"/>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29124,7 @@
       <c r="E319" s="13" t="inlineStr"/>
       <c r="F319" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29152,7 +29152,7 @@
       <c r="E320" s="13" t="inlineStr"/>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29180,7 @@
       <c r="E321" s="13" t="inlineStr"/>
       <c r="F321" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29208,7 +29208,7 @@
       <c r="E322" s="13" t="inlineStr"/>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29236,7 +29236,7 @@
       <c r="E323" s="13" t="inlineStr"/>
       <c r="F323" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29264,7 +29264,7 @@
       <c r="E324" s="13" t="inlineStr"/>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:18</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29292,7 @@
       <c r="E325" s="13" t="inlineStr"/>
       <c r="F325" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -29320,7 +29320,7 @@
       <c r="E326" s="13" t="inlineStr"/>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>22:03:25</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -29348,7 +29348,7 @@
       <c r="E327" s="13" t="inlineStr"/>
       <c r="F327" s="13" t="inlineStr">
         <is>
-          <t>22:03:26</t>
+          <t>22:19:19</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
       <c r="E328" s="13" t="inlineStr"/>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -29404,7 +29404,7 @@
       <c r="E329" s="13" t="inlineStr"/>
       <c r="F329" s="13" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -29432,7 +29432,7 @@
       <c r="E330" s="13" t="inlineStr"/>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -29460,7 +29460,7 @@
       <c r="E331" s="13" t="inlineStr"/>
       <c r="F331" s="13" t="inlineStr">
         <is>
-          <t>22:03:29</t>
+          <t>22:19:22</t>
         </is>
       </c>
     </row>
@@ -29488,7 +29488,7 @@
       <c r="E332" s="13" t="inlineStr"/>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>22:03:30</t>
+          <t>22:19:23</t>
         </is>
       </c>
     </row>
@@ -29516,7 +29516,7 @@
       <c r="E333" s="13" t="inlineStr"/>
       <c r="F333" s="13" t="inlineStr">
         <is>
-          <t>22:03:30</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -29544,7 +29544,7 @@
       <c r="E334" s="13" t="inlineStr"/>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>22:03:31</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -29572,7 +29572,7 @@
       <c r="E335" s="13" t="inlineStr"/>
       <c r="F335" s="13" t="inlineStr">
         <is>
-          <t>22:03:31</t>
+          <t>22:19:24</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29600,7 @@
       <c r="E336" s="13" t="inlineStr"/>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -29628,7 +29628,7 @@
       <c r="E337" s="13" t="inlineStr"/>
       <c r="F337" s="13" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29656,7 @@
       <c r="E338" s="13" t="inlineStr"/>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -29684,7 +29684,7 @@
       <c r="E339" s="13" t="inlineStr"/>
       <c r="F339" s="13" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       <c r="E340" s="13" t="inlineStr"/>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>22:03:32</t>
+          <t>22:19:25</t>
         </is>
       </c>
     </row>
@@ -29740,7 +29740,7 @@
       <c r="E341" s="13" t="inlineStr"/>
       <c r="F341" s="13" t="inlineStr">
         <is>
-          <t>22:03:33</t>
+          <t>22:19:27</t>
         </is>
       </c>
     </row>
@@ -29768,7 +29768,7 @@
       <c r="E342" s="13" t="inlineStr"/>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>22:03:33</t>
+          <t>22:19:27</t>
         </is>
       </c>
     </row>
@@ -29796,7 +29796,7 @@
       <c r="E343" s="13" t="inlineStr"/>
       <c r="F343" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       <c r="E344" s="13" t="inlineStr"/>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29852,7 +29852,7 @@
       <c r="E345" s="13" t="inlineStr"/>
       <c r="F345" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29880,7 +29880,7 @@
       <c r="E346" s="13" t="inlineStr"/>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29908,7 +29908,7 @@
       <c r="E347" s="13" t="inlineStr"/>
       <c r="F347" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29936,7 +29936,7 @@
       <c r="E348" s="13" t="inlineStr"/>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>22:03:35</t>
+          <t>22:19:28</t>
         </is>
       </c>
     </row>
@@ -29964,7 +29964,7 @@
       <c r="E349" s="13" t="inlineStr"/>
       <c r="F349" s="13" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -29992,7 +29992,7 @@
       <c r="E350" s="13" t="inlineStr"/>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -30020,7 +30020,7 @@
       <c r="E351" s="13" t="inlineStr"/>
       <c r="F351" s="13" t="inlineStr">
         <is>
-          <t>22:03:38</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -30048,7 +30048,7 @@
       <c r="E352" s="13" t="inlineStr"/>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -30076,7 +30076,7 @@
       <c r="E353" s="13" t="inlineStr"/>
       <c r="F353" s="13" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30104,7 @@
       <c r="E354" s="13" t="inlineStr"/>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>22:03:39</t>
+          <t>22:19:32</t>
         </is>
       </c>
     </row>
@@ -30132,7 +30132,7 @@
       <c r="E355" s="13" t="inlineStr"/>
       <c r="F355" s="13" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:33</t>
         </is>
       </c>
     </row>
@@ -30160,7 +30160,7 @@
       <c r="E356" s="13" t="inlineStr"/>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:33</t>
         </is>
       </c>
     </row>
@@ -30188,7 +30188,7 @@
       <c r="E357" s="13" t="inlineStr"/>
       <c r="F357" s="13" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30216,7 @@
       <c r="E358" s="13" t="inlineStr"/>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30244,7 +30244,7 @@
       <c r="E359" s="13" t="inlineStr"/>
       <c r="F359" s="13" t="inlineStr">
         <is>
-          <t>22:03:40</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30272,7 +30272,7 @@
       <c r="E360" s="13" t="inlineStr"/>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30300,7 @@
       <c r="E361" s="13" t="inlineStr"/>
       <c r="F361" s="13" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30328,7 +30328,7 @@
       <c r="E362" s="13" t="inlineStr"/>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30356,7 +30356,7 @@
       <c r="E363" s="13" t="inlineStr"/>
       <c r="F363" s="13" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30384,7 +30384,7 @@
       <c r="E364" s="13" t="inlineStr"/>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>22:03:41</t>
+          <t>22:19:34</t>
         </is>
       </c>
     </row>
@@ -30412,7 +30412,7 @@
       <c r="E365" s="13" t="inlineStr"/>
       <c r="F365" s="13" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
       <c r="E366" s="13" t="inlineStr"/>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       <c r="E367" s="13" t="inlineStr"/>
       <c r="F367" s="13" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -30496,7 +30496,7 @@
       <c r="E368" s="13" t="inlineStr"/>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>22:03:42</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -30524,7 +30524,7 @@
       <c r="E369" s="13" t="inlineStr"/>
       <c r="F369" s="13" t="inlineStr">
         <is>
-          <t>22:03:43</t>
+          <t>22:19:36</t>
         </is>
       </c>
     </row>
@@ -30552,7 +30552,7 @@
       <c r="E370" s="13" t="inlineStr"/>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -30580,7 +30580,7 @@
       <c r="E371" s="13" t="inlineStr"/>
       <c r="F371" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       <c r="E372" s="13" t="inlineStr"/>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:39</t>
         </is>
       </c>
     </row>
@@ -30636,7 +30636,7 @@
       <c r="E373" s="13" t="inlineStr"/>
       <c r="F373" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
       <c r="E374" s="13" t="inlineStr"/>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30692,7 @@
       <c r="E375" s="13" t="inlineStr"/>
       <c r="F375" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30720,7 +30720,7 @@
       <c r="E376" s="13" t="inlineStr"/>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>22:03:46</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30748,7 +30748,7 @@
       <c r="E377" s="13" t="inlineStr"/>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30776,7 +30776,7 @@
       <c r="E378" s="13" t="inlineStr"/>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       <c r="E379" s="13" t="inlineStr"/>
       <c r="F379" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
       <c r="E380" s="13" t="inlineStr"/>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30860,7 @@
       <c r="E381" s="13" t="inlineStr"/>
       <c r="F381" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:40</t>
         </is>
       </c>
     </row>
@@ -30888,7 +30888,7 @@
       <c r="E382" s="13" t="inlineStr"/>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -30916,7 +30916,7 @@
       <c r="E383" s="13" t="inlineStr"/>
       <c r="F383" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -30944,7 +30944,7 @@
       <c r="E384" s="13" t="inlineStr"/>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>22:03:47</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -30972,7 +30972,7 @@
       <c r="E385" s="13" t="inlineStr"/>
       <c r="F385" s="13" t="inlineStr">
         <is>
-          <t>22:03:48</t>
+          <t>22:19:41</t>
         </is>
       </c>
     </row>
@@ -31000,7 +31000,7 @@
       <c r="E386" s="13" t="inlineStr"/>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -31028,7 +31028,7 @@
       <c r="E387" s="13" t="inlineStr"/>
       <c r="F387" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -31056,7 +31056,7 @@
       <c r="E388" s="13" t="inlineStr"/>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -31084,7 +31084,7 @@
       <c r="E389" s="13" t="inlineStr"/>
       <c r="F389" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:44</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31112,7 @@
       <c r="E390" s="13" t="inlineStr"/>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       <c r="E391" s="13" t="inlineStr"/>
       <c r="F391" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31168,7 +31168,7 @@
       <c r="E392" s="13" t="inlineStr"/>
       <c r="F392" s="13" t="inlineStr">
         <is>
-          <t>22:03:51</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31196,7 +31196,7 @@
       <c r="E393" s="13" t="inlineStr"/>
       <c r="F393" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       <c r="E394" s="13" t="inlineStr"/>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31252,7 +31252,7 @@
       <c r="E395" s="13" t="inlineStr"/>
       <c r="F395" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31280,7 @@
       <c r="E396" s="13" t="inlineStr"/>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31308,7 +31308,7 @@
       <c r="E397" s="13" t="inlineStr"/>
       <c r="F397" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31336,7 +31336,7 @@
       <c r="E398" s="13" t="inlineStr"/>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:45</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31364,7 @@
       <c r="E399" s="13" t="inlineStr"/>
       <c r="F399" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       <c r="E400" s="13" t="inlineStr"/>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       <c r="E401" s="13" t="inlineStr"/>
       <c r="F401" s="13" t="inlineStr">
         <is>
-          <t>22:03:52</t>
+          <t>22:19:46</t>
         </is>
       </c>
     </row>

--- a/tests/ev_test_report.xlsx
+++ b/tests/ev_test_report.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26 22:19:48</t>
+          <t>2026-07-08 10:25:58</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>https://dist-taupe-chi-67.vercel.app</t>
+          <t>http://localhost:3000</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="I2" s="9" t="inlineStr"/>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:30</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:30</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       <c r="I15" s="11" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       <c r="I16" s="9" t="inlineStr"/>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       <c r="I19" s="11" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       <c r="I20" s="9" t="inlineStr"/>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       <c r="I22" s="9" t="inlineStr"/>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       <c r="I24" s="9" t="inlineStr"/>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       <c r="I34" s="9" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       <c r="I35" s="11" t="inlineStr"/>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       <c r="I39" s="11" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       <c r="I43" s="11" t="inlineStr"/>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       <c r="I45" s="11" t="inlineStr"/>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       <c r="I47" s="11" t="inlineStr"/>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       <c r="I51" s="11" t="inlineStr"/>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       <c r="I52" s="9" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       <c r="I53" s="11" t="inlineStr"/>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       <c r="I55" s="11" t="inlineStr"/>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       <c r="I56" s="9" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>22:15:35</t>
+          <t>10:21:46</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       <c r="I57" s="11" t="inlineStr"/>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>22:15:40</t>
+          <t>10:21:51</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>22:15:46</t>
+          <t>10:21:57</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>22:15:53</t>
+          <t>10:22:04</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>22:15:58</t>
+          <t>10:22:09</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>22:16:03</t>
+          <t>10:22:14</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>22:16:08</t>
+          <t>10:22:19</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>22:16:14</t>
+          <t>10:22:24</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>22:16:16</t>
+          <t>10:22:26</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       <c r="I65" s="11" t="inlineStr"/>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>22:16:19</t>
+          <t>10:22:30</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       <c r="I66" s="9" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>22:16:24</t>
+          <t>10:22:35</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       <c r="I67" s="11" t="inlineStr"/>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>22:16:24</t>
+          <t>10:22:35</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>22:16:31</t>
+          <t>10:22:42</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       <c r="I69" s="11" t="inlineStr"/>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>22:16:33</t>
+          <t>10:22:44</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       <c r="I70" s="9" t="inlineStr"/>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>22:16:42</t>
+          <t>10:22:52</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       <c r="I71" s="11" t="inlineStr"/>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>10:22:57</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       <c r="I72" s="9" t="inlineStr"/>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>10:22:58</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       <c r="I73" s="11" t="inlineStr"/>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>22:16:52</t>
+          <t>10:23:03</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       <c r="I74" s="9" t="inlineStr"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>22:16:52</t>
+          <t>10:23:03</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       <c r="I75" s="11" t="inlineStr"/>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>22:16:58</t>
+          <t>10:23:09</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       <c r="I76" s="9" t="inlineStr"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>22:17:03</t>
+          <t>10:23:14</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       <c r="I77" s="11" t="inlineStr"/>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>22:17:06</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       <c r="I78" s="9" t="inlineStr"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       <c r="I79" s="11" t="inlineStr"/>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       <c r="I81" s="11" t="inlineStr"/>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       <c r="I82" s="9" t="inlineStr"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       <c r="I83" s="11" t="inlineStr"/>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>22:17:13</t>
+          <t>10:23:23</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       <c r="I84" s="9" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>22:17:15</t>
+          <t>10:23:25</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       <c r="I85" s="11" t="inlineStr"/>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>22:17:18</t>
+          <t>10:23:28</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       <c r="I86" s="9" t="inlineStr"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>22:17:18</t>
+          <t>10:23:28</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       <c r="I87" s="11" t="inlineStr"/>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>22:17:24</t>
+          <t>10:23:34</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       <c r="I88" s="9" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>22:17:26</t>
+          <t>10:23:36</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       <c r="I89" s="11" t="inlineStr"/>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>22:17:29</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       <c r="I90" s="9" t="inlineStr"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>22:17:29</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       <c r="I91" s="11" t="inlineStr"/>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       <c r="I93" s="11" t="inlineStr"/>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       <c r="I95" s="11" t="inlineStr"/>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>22:17:36</t>
+          <t>10:23:45</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>22:17:38</t>
+          <t>10:23:48</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       <c r="I97" s="11" t="inlineStr"/>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>22:17:51</t>
+          <t>10:23:58</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>22:17:51</t>
+          <t>10:23:58</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       <c r="I99" s="11" t="inlineStr"/>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       <c r="I101" s="11" t="inlineStr"/>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       <c r="I103" s="11" t="inlineStr"/>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       <c r="I104" s="9" t="inlineStr"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       <c r="I105" s="11" t="inlineStr"/>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       <c r="I106" s="9" t="inlineStr"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>22:17:53</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       <c r="I107" s="11" t="inlineStr"/>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>22:17:53</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       <c r="I108" s="9" t="inlineStr"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>22:18:03</t>
+          <t>10:24:10</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       <c r="I109" s="11" t="inlineStr"/>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>22:18:03</t>
+          <t>10:24:10</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       <c r="I110" s="9" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       <c r="I111" s="11" t="inlineStr"/>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       <c r="I112" s="9" t="inlineStr"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       <c r="I113" s="11" t="inlineStr"/>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       <c r="I114" s="9" t="inlineStr"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="I115" s="11" t="inlineStr"/>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       <c r="I117" s="11" t="inlineStr"/>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       <c r="I119" s="11" t="inlineStr"/>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       <c r="I120" s="9" t="inlineStr"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       <c r="I121" s="11" t="inlineStr"/>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       <c r="I122" s="9" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       <c r="I123" s="11" t="inlineStr"/>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       <c r="I124" s="9" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       <c r="I125" s="11" t="inlineStr"/>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       <c r="I126" s="9" t="inlineStr"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       <c r="I127" s="11" t="inlineStr"/>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       <c r="I128" s="9" t="inlineStr"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       <c r="I129" s="11" t="inlineStr"/>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       <c r="I130" s="9" t="inlineStr"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       <c r="I131" s="11" t="inlineStr"/>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       <c r="I132" s="9" t="inlineStr"/>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       <c r="I133" s="11" t="inlineStr"/>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:23</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       <c r="I134" s="9" t="inlineStr"/>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       <c r="I135" s="11" t="inlineStr"/>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       <c r="I136" s="9" t="inlineStr"/>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       <c r="I137" s="11" t="inlineStr"/>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       <c r="I138" s="9" t="inlineStr"/>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       <c r="I139" s="11" t="inlineStr"/>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       <c r="I140" s="9" t="inlineStr"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       <c r="I141" s="11" t="inlineStr"/>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       <c r="I142" s="9" t="inlineStr"/>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       <c r="I143" s="11" t="inlineStr"/>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       <c r="I144" s="9" t="inlineStr"/>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       <c r="I145" s="11" t="inlineStr"/>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       <c r="I146" s="9" t="inlineStr"/>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       <c r="I147" s="11" t="inlineStr"/>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       <c r="I148" s="9" t="inlineStr"/>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
       <c r="I149" s="11" t="inlineStr"/>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:28</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       <c r="I150" s="9" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>22:18:22</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="I151" s="11" t="inlineStr"/>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>22:18:22</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       <c r="I152" s="9" t="inlineStr"/>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="I153" s="11" t="inlineStr"/>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       <c r="I154" s="9" t="inlineStr"/>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       <c r="I155" s="11" t="inlineStr"/>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       <c r="I156" s="9" t="inlineStr"/>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       <c r="I157" s="11" t="inlineStr"/>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       <c r="I158" s="9" t="inlineStr"/>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       <c r="I159" s="11" t="inlineStr"/>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       <c r="I160" s="9" t="inlineStr"/>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       <c r="I161" s="11" t="inlineStr"/>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       <c r="I162" s="9" t="inlineStr"/>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       <c r="I163" s="11" t="inlineStr"/>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       <c r="I164" s="9" t="inlineStr"/>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>22:18:25</t>
+          <t>10:24:31</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       <c r="I165" s="11" t="inlineStr"/>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>22:18:25</t>
+          <t>10:24:32</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       <c r="I166" s="9" t="inlineStr"/>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       <c r="I167" s="11" t="inlineStr"/>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       <c r="I168" s="9" t="inlineStr"/>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       <c r="I169" s="11" t="inlineStr"/>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       <c r="I170" s="9" t="inlineStr"/>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       <c r="I171" s="11" t="inlineStr"/>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       <c r="I172" s="9" t="inlineStr"/>
       <c r="J172" s="9" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       <c r="I173" s="11" t="inlineStr"/>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       <c r="I174" s="9" t="inlineStr"/>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9315,7 +9315,7 @@
       <c r="I175" s="11" t="inlineStr"/>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       <c r="I176" s="9" t="inlineStr"/>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       <c r="I177" s="11" t="inlineStr"/>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       <c r="I178" s="9" t="inlineStr"/>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       <c r="I179" s="11" t="inlineStr"/>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       <c r="I180" s="9" t="inlineStr"/>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
       <c r="I181" s="11" t="inlineStr"/>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       <c r="I182" s="9" t="inlineStr"/>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       <c r="I183" s="11" t="inlineStr"/>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       <c r="I184" s="9" t="inlineStr"/>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       <c r="I185" s="11" t="inlineStr"/>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       <c r="I186" s="9" t="inlineStr"/>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
       <c r="I187" s="11" t="inlineStr"/>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       <c r="I188" s="9" t="inlineStr"/>
       <c r="J188" s="9" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       <c r="I189" s="11" t="inlineStr"/>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       <c r="I190" s="9" t="inlineStr"/>
       <c r="J190" s="9" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -10083,7 +10083,7 @@
       <c r="I191" s="11" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
       <c r="I192" s="9" t="inlineStr"/>
       <c r="J192" s="9" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       <c r="I194" s="9" t="inlineStr"/>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
       <c r="I195" s="11" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       <c r="I196" s="9" t="inlineStr"/>
       <c r="J196" s="9" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       <c r="I197" s="11" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       <c r="I198" s="9" t="inlineStr"/>
       <c r="J198" s="9" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:43</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10467,7 @@
       <c r="I199" s="11" t="inlineStr"/>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:43</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       <c r="I200" s="9" t="inlineStr"/>
       <c r="J200" s="9" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       <c r="I201" s="11" t="inlineStr"/>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       <c r="I202" s="9" t="inlineStr"/>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       <c r="I203" s="11" t="inlineStr"/>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       <c r="I204" s="9" t="inlineStr"/>
       <c r="J204" s="9" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10755,7 +10755,7 @@
       <c r="I205" s="11" t="inlineStr"/>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       <c r="I206" s="9" t="inlineStr"/>
       <c r="J206" s="9" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       <c r="I207" s="11" t="inlineStr"/>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       <c r="I208" s="9" t="inlineStr"/>
       <c r="J208" s="9" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -10947,7 +10947,7 @@
       <c r="I209" s="11" t="inlineStr"/>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       <c r="I210" s="9" t="inlineStr"/>
       <c r="J210" s="9" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       <c r="I211" s="11" t="inlineStr"/>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       <c r="I212" s="9" t="inlineStr"/>
       <c r="J212" s="9" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       <c r="I213" s="11" t="inlineStr"/>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       <c r="I214" s="9" t="inlineStr"/>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       <c r="I215" s="11" t="inlineStr"/>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       <c r="I216" s="9" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       <c r="I217" s="11" t="inlineStr"/>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       <c r="I218" s="9" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       <c r="I219" s="11" t="inlineStr"/>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       <c r="I220" s="9" t="inlineStr"/>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       <c r="I221" s="11" t="inlineStr"/>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       <c r="I222" s="9" t="inlineStr"/>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       <c r="I223" s="11" t="inlineStr"/>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11667,7 @@
       <c r="I224" s="9" t="inlineStr"/>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       <c r="I225" s="11" t="inlineStr"/>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       <c r="I226" s="9" t="inlineStr"/>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       <c r="I227" s="11" t="inlineStr"/>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       <c r="I228" s="9" t="inlineStr"/>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       <c r="I229" s="11" t="inlineStr"/>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       <c r="I230" s="9" t="inlineStr"/>
       <c r="J230" s="9" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       <c r="I231" s="11" t="inlineStr"/>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       <c r="I232" s="9" t="inlineStr"/>
       <c r="J232" s="9" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       <c r="I233" s="11" t="inlineStr"/>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12147,7 @@
       <c r="I234" s="9" t="inlineStr"/>
       <c r="J234" s="9" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       <c r="I235" s="11" t="inlineStr"/>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       <c r="I236" s="9" t="inlineStr"/>
       <c r="J236" s="9" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       <c r="I237" s="11" t="inlineStr"/>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       <c r="I238" s="9" t="inlineStr"/>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       <c r="I239" s="11" t="inlineStr"/>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       <c r="I240" s="9" t="inlineStr"/>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12483,7 +12483,7 @@
       <c r="I241" s="11" t="inlineStr"/>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       <c r="I242" s="9" t="inlineStr"/>
       <c r="J242" s="9" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       <c r="I243" s="11" t="inlineStr"/>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       <c r="I244" s="9" t="inlineStr"/>
       <c r="J244" s="9" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       <c r="I245" s="11" t="inlineStr"/>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       <c r="I246" s="9" t="inlineStr"/>
       <c r="J246" s="9" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       <c r="I247" s="11" t="inlineStr"/>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       <c r="I248" s="9" t="inlineStr"/>
       <c r="J248" s="9" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12867,7 +12867,7 @@
       <c r="I249" s="11" t="inlineStr"/>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12915,7 @@
       <c r="I250" s="9" t="inlineStr"/>
       <c r="J250" s="9" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       <c r="I251" s="11" t="inlineStr"/>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
       <c r="I252" s="9" t="inlineStr"/>
       <c r="J252" s="9" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       <c r="I253" s="11" t="inlineStr"/>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       <c r="I254" s="9" t="inlineStr"/>
       <c r="J254" s="9" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -13155,7 +13155,7 @@
       <c r="I255" s="11" t="inlineStr"/>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13203,7 @@
       <c r="I256" s="9" t="inlineStr"/>
       <c r="J256" s="9" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       <c r="I257" s="11" t="inlineStr"/>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>22:18:50</t>
+          <t>10:24:56</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13299,7 @@
       <c r="I258" s="9" t="inlineStr"/>
       <c r="J258" s="9" t="inlineStr">
         <is>
-          <t>22:18:53</t>
+          <t>10:24:59</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       <c r="I259" s="11" t="inlineStr"/>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>22:18:53</t>
+          <t>10:24:59</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       <c r="I260" s="9" t="inlineStr"/>
       <c r="J260" s="9" t="inlineStr">
         <is>
-          <t>22:18:54</t>
+          <t>10:25:00</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13443,7 @@
       <c r="I261" s="11" t="inlineStr"/>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>22:18:54</t>
+          <t>10:25:00</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       <c r="I262" s="9" t="inlineStr"/>
       <c r="J262" s="9" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       <c r="I263" s="11" t="inlineStr"/>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       <c r="I264" s="9" t="inlineStr"/>
       <c r="J264" s="9" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       <c r="I265" s="11" t="inlineStr"/>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       <c r="I266" s="9" t="inlineStr"/>
       <c r="J266" s="9" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13731,7 @@
       <c r="I267" s="11" t="inlineStr"/>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       <c r="I268" s="9" t="inlineStr"/>
       <c r="J268" s="9" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       <c r="I269" s="11" t="inlineStr"/>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
       <c r="I270" s="9" t="inlineStr"/>
       <c r="J270" s="9" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13923,7 @@
       <c r="I271" s="11" t="inlineStr"/>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -13971,7 +13971,7 @@
       <c r="I272" s="9" t="inlineStr"/>
       <c r="J272" s="9" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       <c r="I273" s="11" t="inlineStr"/>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       <c r="I274" s="9" t="inlineStr"/>
       <c r="J274" s="9" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       <c r="I275" s="11" t="inlineStr"/>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>22:19:01</t>
+          <t>10:25:06</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       <c r="I276" s="9" t="inlineStr"/>
       <c r="J276" s="9" t="inlineStr">
         <is>
-          <t>22:19:01</t>
+          <t>10:25:07</t>
         </is>
       </c>
     </row>
@@ -14211,7 +14211,7 @@
       <c r="I277" s="11" t="inlineStr"/>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       <c r="I278" s="9" t="inlineStr"/>
       <c r="J278" s="9" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14307,7 +14307,7 @@
       <c r="I279" s="11" t="inlineStr"/>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       <c r="I280" s="9" t="inlineStr"/>
       <c r="J280" s="9" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       <c r="I281" s="11" t="inlineStr"/>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       <c r="I282" s="9" t="inlineStr"/>
       <c r="J282" s="9" t="inlineStr">
         <is>
-          <t>22:19:04</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14499,7 +14499,7 @@
       <c r="I283" s="11" t="inlineStr"/>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>22:19:04</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       <c r="I284" s="9" t="inlineStr"/>
       <c r="J284" s="9" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       <c r="I285" s="11" t="inlineStr"/>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       <c r="I286" s="9" t="inlineStr"/>
       <c r="J286" s="9" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       <c r="I287" s="11" t="inlineStr"/>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       <c r="I288" s="9" t="inlineStr"/>
       <c r="J288" s="9" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       <c r="I289" s="11" t="inlineStr"/>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:14</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       <c r="I290" s="9" t="inlineStr"/>
       <c r="J290" s="9" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:14</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14883,7 @@
       <c r="I291" s="11" t="inlineStr"/>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:16</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
       <c r="I292" s="9" t="inlineStr"/>
       <c r="J292" s="9" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:17</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       <c r="I293" s="11" t="inlineStr"/>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:18</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       <c r="I294" s="9" t="inlineStr"/>
       <c r="J294" s="9" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:18</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       <c r="I295" s="11" t="inlineStr"/>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15123,7 @@
       <c r="I296" s="9" t="inlineStr"/>
       <c r="J296" s="9" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       <c r="I297" s="11" t="inlineStr"/>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       <c r="I298" s="9" t="inlineStr"/>
       <c r="J298" s="9" t="inlineStr">
         <is>
-          <t>22:19:10</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       <c r="I299" s="11" t="inlineStr"/>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       <c r="I300" s="9" t="inlineStr"/>
       <c r="J300" s="9" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       <c r="I301" s="11" t="inlineStr"/>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       <c r="I302" s="9" t="inlineStr"/>
       <c r="J302" s="9" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       <c r="I303" s="11" t="inlineStr"/>
       <c r="J303" s="11" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       <c r="I304" s="9" t="inlineStr"/>
       <c r="J304" s="9" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       <c r="I305" s="11" t="inlineStr"/>
       <c r="J305" s="11" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       <c r="I306" s="9" t="inlineStr"/>
       <c r="J306" s="9" t="inlineStr">
         <is>
-          <t>22:19:14</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       <c r="I307" s="11" t="inlineStr"/>
       <c r="J307" s="11" t="inlineStr">
         <is>
-          <t>22:19:14</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -15699,7 +15699,7 @@
       <c r="I308" s="9" t="inlineStr"/>
       <c r="J308" s="9" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -15747,7 +15747,7 @@
       <c r="I309" s="11" t="inlineStr"/>
       <c r="J309" s="11" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -15795,7 +15795,7 @@
       <c r="I310" s="9" t="inlineStr"/>
       <c r="J310" s="9" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:25</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       <c r="I311" s="11" t="inlineStr"/>
       <c r="J311" s="11" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:25</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       <c r="I312" s="9" t="inlineStr"/>
       <c r="J312" s="9" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       <c r="I313" s="11" t="inlineStr"/>
       <c r="J313" s="11" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -15987,7 +15987,7 @@
       <c r="I314" s="9" t="inlineStr"/>
       <c r="J314" s="9" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16035,7 @@
       <c r="I315" s="11" t="inlineStr"/>
       <c r="J315" s="11" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
       <c r="I316" s="9" t="inlineStr"/>
       <c r="J316" s="9" t="inlineStr">
         <is>
-          <t>22:19:17</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       <c r="I317" s="11" t="inlineStr"/>
       <c r="J317" s="11" t="inlineStr">
         <is>
-          <t>22:19:17</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       <c r="I318" s="9" t="inlineStr"/>
       <c r="J318" s="9" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       <c r="I319" s="11" t="inlineStr"/>
       <c r="J319" s="11" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       <c r="I320" s="9" t="inlineStr"/>
       <c r="J320" s="9" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       <c r="I321" s="11" t="inlineStr"/>
       <c r="J321" s="11" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16371,7 @@
       <c r="I322" s="9" t="inlineStr"/>
       <c r="J322" s="9" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16419,7 @@
       <c r="I323" s="11" t="inlineStr"/>
       <c r="J323" s="11" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16467,7 @@
       <c r="I324" s="9" t="inlineStr"/>
       <c r="J324" s="9" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       <c r="I325" s="11" t="inlineStr"/>
       <c r="J325" s="11" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       <c r="I326" s="9" t="inlineStr"/>
       <c r="J326" s="9" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       <c r="I327" s="11" t="inlineStr"/>
       <c r="J327" s="11" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:29</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       <c r="I328" s="9" t="inlineStr"/>
       <c r="J328" s="9" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       <c r="I329" s="11" t="inlineStr"/>
       <c r="J329" s="11" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -16755,7 +16755,7 @@
       <c r="I330" s="9" t="inlineStr"/>
       <c r="J330" s="9" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -16803,7 +16803,7 @@
       <c r="I331" s="11" t="inlineStr"/>
       <c r="J331" s="11" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -16851,7 +16851,7 @@
       <c r="I332" s="9" t="inlineStr"/>
       <c r="J332" s="9" t="inlineStr">
         <is>
-          <t>22:19:23</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       <c r="I333" s="11" t="inlineStr"/>
       <c r="J333" s="11" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16947,7 @@
       <c r="I334" s="9" t="inlineStr"/>
       <c r="J334" s="9" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       <c r="I335" s="11" t="inlineStr"/>
       <c r="J335" s="11" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:34</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17043,7 @@
       <c r="I336" s="9" t="inlineStr"/>
       <c r="J336" s="9" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -17091,7 +17091,7 @@
       <c r="I337" s="11" t="inlineStr"/>
       <c r="J337" s="11" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -17139,7 +17139,7 @@
       <c r="I338" s="9" t="inlineStr"/>
       <c r="J338" s="9" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17187,7 @@
       <c r="I339" s="11" t="inlineStr"/>
       <c r="J339" s="11" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -17235,7 +17235,7 @@
       <c r="I340" s="9" t="inlineStr"/>
       <c r="J340" s="9" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       <c r="I341" s="11" t="inlineStr"/>
       <c r="J341" s="11" t="inlineStr">
         <is>
-          <t>22:19:27</t>
+          <t>10:25:36</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       <c r="I342" s="9" t="inlineStr"/>
       <c r="J342" s="9" t="inlineStr">
         <is>
-          <t>22:19:27</t>
+          <t>10:25:36</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
       <c r="I343" s="11" t="inlineStr"/>
       <c r="J343" s="11" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:37</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       <c r="I344" s="9" t="inlineStr"/>
       <c r="J344" s="9" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
       <c r="I345" s="11" t="inlineStr"/>
       <c r="J345" s="11" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17523,7 @@
       <c r="I346" s="9" t="inlineStr"/>
       <c r="J346" s="9" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -17571,7 +17571,7 @@
       <c r="I347" s="11" t="inlineStr"/>
       <c r="J347" s="11" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       <c r="I348" s="9" t="inlineStr"/>
       <c r="J348" s="9" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -17667,7 +17667,7 @@
       <c r="I349" s="11" t="inlineStr"/>
       <c r="J349" s="11" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       <c r="I350" s="9" t="inlineStr"/>
       <c r="J350" s="9" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       <c r="I351" s="11" t="inlineStr"/>
       <c r="J351" s="11" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       <c r="I352" s="9" t="inlineStr"/>
       <c r="J352" s="9" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       <c r="I353" s="11" t="inlineStr"/>
       <c r="J353" s="11" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -17907,7 +17907,7 @@
       <c r="I354" s="9" t="inlineStr"/>
       <c r="J354" s="9" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       <c r="I355" s="11" t="inlineStr"/>
       <c r="J355" s="11" t="inlineStr">
         <is>
-          <t>22:19:33</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       <c r="I356" s="9" t="inlineStr"/>
       <c r="J356" s="9" t="inlineStr">
         <is>
-          <t>22:19:33</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
       <c r="I357" s="11" t="inlineStr"/>
       <c r="J357" s="11" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18099,7 +18099,7 @@
       <c r="I358" s="9" t="inlineStr"/>
       <c r="J358" s="9" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18147,7 @@
       <c r="I359" s="11" t="inlineStr"/>
       <c r="J359" s="11" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18195,7 @@
       <c r="I360" s="9" t="inlineStr"/>
       <c r="J360" s="9" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18243,7 @@
       <c r="I361" s="11" t="inlineStr"/>
       <c r="J361" s="11" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       <c r="I362" s="9" t="inlineStr"/>
       <c r="J362" s="9" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -18339,7 +18339,7 @@
       <c r="I363" s="11" t="inlineStr"/>
       <c r="J363" s="11" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
       <c r="I364" s="9" t="inlineStr"/>
       <c r="J364" s="9" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       <c r="I365" s="11" t="inlineStr"/>
       <c r="J365" s="11" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
       <c r="I366" s="9" t="inlineStr"/>
       <c r="J366" s="9" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18531,7 @@
       <c r="I367" s="11" t="inlineStr"/>
       <c r="J367" s="11" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       <c r="I368" s="9" t="inlineStr"/>
       <c r="J368" s="9" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       <c r="I369" s="11" t="inlineStr"/>
       <c r="J369" s="11" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:46</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       <c r="I370" s="9" t="inlineStr"/>
       <c r="J370" s="9" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       <c r="I371" s="11" t="inlineStr"/>
       <c r="J371" s="11" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
       <c r="I372" s="9" t="inlineStr"/>
       <c r="J372" s="9" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       <c r="I373" s="11" t="inlineStr"/>
       <c r="J373" s="11" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       <c r="I374" s="9" t="inlineStr"/>
       <c r="J374" s="9" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18915,7 @@
       <c r="I375" s="11" t="inlineStr"/>
       <c r="J375" s="11" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -18963,7 +18963,7 @@
       <c r="I376" s="9" t="inlineStr"/>
       <c r="J376" s="9" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       <c r="I377" s="11" t="inlineStr"/>
       <c r="J377" s="11" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       <c r="I378" s="9" t="inlineStr"/>
       <c r="J378" s="9" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       <c r="I379" s="11" t="inlineStr"/>
       <c r="J379" s="11" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       <c r="I380" s="9" t="inlineStr"/>
       <c r="J380" s="9" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19203,7 +19203,7 @@
       <c r="I381" s="11" t="inlineStr"/>
       <c r="J381" s="11" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19251,7 @@
       <c r="I382" s="9" t="inlineStr"/>
       <c r="J382" s="9" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       <c r="I383" s="11" t="inlineStr"/>
       <c r="J383" s="11" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19347,7 @@
       <c r="I384" s="9" t="inlineStr"/>
       <c r="J384" s="9" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -19395,7 +19395,7 @@
       <c r="I385" s="11" t="inlineStr"/>
       <c r="J385" s="11" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:51</t>
         </is>
       </c>
     </row>
@@ -19443,7 +19443,7 @@
       <c r="I386" s="9" t="inlineStr"/>
       <c r="J386" s="9" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       <c r="I387" s="11" t="inlineStr"/>
       <c r="J387" s="11" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       <c r="I388" s="9" t="inlineStr"/>
       <c r="J388" s="9" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19587,7 +19587,7 @@
       <c r="I389" s="11" t="inlineStr"/>
       <c r="J389" s="11" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       <c r="I390" s="9" t="inlineStr"/>
       <c r="J390" s="9" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       <c r="I391" s="11" t="inlineStr"/>
       <c r="J391" s="11" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19732,7 @@
       <c r="I392" s="9" t="inlineStr"/>
       <c r="J392" s="9" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       <c r="I393" s="11" t="inlineStr"/>
       <c r="J393" s="11" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19828,7 @@
       <c r="I394" s="9" t="inlineStr"/>
       <c r="J394" s="9" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       <c r="I395" s="11" t="inlineStr"/>
       <c r="J395" s="11" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       <c r="I396" s="9" t="inlineStr"/>
       <c r="J396" s="9" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -19973,7 +19973,7 @@
       <c r="I397" s="11" t="inlineStr"/>
       <c r="J397" s="11" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -20021,7 +20021,7 @@
       <c r="I398" s="9" t="inlineStr"/>
       <c r="J398" s="9" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -20069,7 +20069,7 @@
       <c r="I399" s="11" t="inlineStr"/>
       <c r="J399" s="11" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       <c r="I400" s="9" t="inlineStr"/>
       <c r="J400" s="9" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
       <c r="I401" s="11" t="inlineStr"/>
       <c r="J401" s="11" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20248,7 @@
       <c r="E2" s="13" t="inlineStr"/>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:30</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20276,7 @@
       <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:30</t>
         </is>
       </c>
     </row>
@@ -20304,7 +20304,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20332,7 @@
       <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>22:15:18</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20360,7 @@
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20416,7 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20444,7 +20444,7 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20472,7 +20472,7 @@
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20500,7 +20500,7 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>22:15:19</t>
+          <t>10:21:31</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20612,7 @@
       <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>22:15:20</t>
+          <t>10:21:32</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20696,7 @@
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>22:15:23</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:35</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20780,7 +20780,7 @@
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20836,7 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20864,7 +20864,7 @@
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>22:15:24</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20892,7 @@
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20920,7 +20920,7 @@
       <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -20976,7 +20976,7 @@
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:36</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -21060,7 +21060,7 @@
       <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>22:15:25</t>
+          <t>10:21:37</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
       <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21144,7 @@
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21200,7 @@
       <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -21228,7 +21228,7 @@
       <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:40</t>
         </is>
       </c>
     </row>
@@ -21256,7 +21256,7 @@
       <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>22:15:29</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21312,7 +21312,7 @@
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
       <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21452,7 @@
       <c r="E45" s="13" t="inlineStr"/>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21480,7 +21480,7 @@
       <c r="E46" s="13" t="inlineStr"/>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:41</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       <c r="E47" s="13" t="inlineStr"/>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>22:15:30</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       <c r="E48" s="13" t="inlineStr"/>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21564,7 +21564,7 @@
       <c r="E49" s="13" t="inlineStr"/>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21592,7 +21592,7 @@
       <c r="E50" s="13" t="inlineStr"/>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       <c r="E51" s="13" t="inlineStr"/>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21648,7 +21648,7 @@
       <c r="E52" s="13" t="inlineStr"/>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>22:15:31</t>
+          <t>10:21:42</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21676,7 @@
       <c r="E53" s="13" t="inlineStr"/>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -21704,7 +21704,7 @@
       <c r="E54" s="13" t="inlineStr"/>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -21732,7 +21732,7 @@
       <c r="E55" s="13" t="inlineStr"/>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>22:15:34</t>
+          <t>10:21:45</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       <c r="E56" s="13" t="inlineStr"/>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>22:15:35</t>
+          <t>10:21:46</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21788,7 @@
       <c r="E57" s="13" t="inlineStr"/>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>22:15:40</t>
+          <t>10:21:51</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21816,7 @@
       <c r="E58" s="13" t="inlineStr"/>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>22:15:46</t>
+          <t>10:21:57</t>
         </is>
       </c>
     </row>
@@ -21844,7 +21844,7 @@
       <c r="E59" s="13" t="inlineStr"/>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>22:15:53</t>
+          <t>10:22:04</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       <c r="E60" s="13" t="inlineStr"/>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>22:15:58</t>
+          <t>10:22:09</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       <c r="E61" s="13" t="inlineStr"/>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>22:16:03</t>
+          <t>10:22:14</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>22:16:08</t>
+          <t>10:22:19</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       <c r="E63" s="13" t="inlineStr"/>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>22:16:14</t>
+          <t>10:22:24</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       <c r="E64" s="13" t="inlineStr"/>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>22:16:16</t>
+          <t>10:22:26</t>
         </is>
       </c>
     </row>
@@ -22012,7 +22012,7 @@
       <c r="E65" s="13" t="inlineStr"/>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>22:16:19</t>
+          <t>10:22:30</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
       <c r="E66" s="13" t="inlineStr"/>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>22:16:24</t>
+          <t>10:22:35</t>
         </is>
       </c>
     </row>
@@ -22068,7 +22068,7 @@
       <c r="E67" s="13" t="inlineStr"/>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>22:16:24</t>
+          <t>10:22:35</t>
         </is>
       </c>
     </row>
@@ -22096,7 +22096,7 @@
       <c r="E68" s="13" t="inlineStr"/>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>22:16:31</t>
+          <t>10:22:42</t>
         </is>
       </c>
     </row>
@@ -22124,7 +22124,7 @@
       <c r="E69" s="13" t="inlineStr"/>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>22:16:33</t>
+          <t>10:22:44</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       <c r="E70" s="13" t="inlineStr"/>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>22:16:42</t>
+          <t>10:22:52</t>
         </is>
       </c>
     </row>
@@ -22180,7 +22180,7 @@
       <c r="E71" s="13" t="inlineStr"/>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>10:22:57</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22208,7 @@
       <c r="E72" s="13" t="inlineStr"/>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>10:22:58</t>
         </is>
       </c>
     </row>
@@ -22236,7 +22236,7 @@
       <c r="E73" s="13" t="inlineStr"/>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>22:16:52</t>
+          <t>10:23:03</t>
         </is>
       </c>
     </row>
@@ -22264,7 +22264,7 @@
       <c r="E74" s="13" t="inlineStr"/>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>22:16:52</t>
+          <t>10:23:03</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       <c r="E75" s="13" t="inlineStr"/>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>22:16:58</t>
+          <t>10:23:09</t>
         </is>
       </c>
     </row>
@@ -22320,7 +22320,7 @@
       <c r="E76" s="13" t="inlineStr"/>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>22:17:03</t>
+          <t>10:23:14</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22348,7 @@
       <c r="E77" s="13" t="inlineStr"/>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>22:17:06</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22376,7 @@
       <c r="E78" s="13" t="inlineStr"/>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22404,7 +22404,7 @@
       <c r="E79" s="13" t="inlineStr"/>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       <c r="E80" s="13" t="inlineStr"/>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22460,7 +22460,7 @@
       <c r="E81" s="13" t="inlineStr"/>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22488,7 +22488,7 @@
       <c r="E82" s="13" t="inlineStr"/>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>22:17:07</t>
+          <t>10:23:17</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
       <c r="E83" s="13" t="inlineStr"/>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>22:17:13</t>
+          <t>10:23:23</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       <c r="E84" s="13" t="inlineStr"/>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>22:17:15</t>
+          <t>10:23:25</t>
         </is>
       </c>
     </row>
@@ -22572,7 +22572,7 @@
       <c r="E85" s="13" t="inlineStr"/>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>22:17:18</t>
+          <t>10:23:28</t>
         </is>
       </c>
     </row>
@@ -22600,7 +22600,7 @@
       <c r="E86" s="13" t="inlineStr"/>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>22:17:18</t>
+          <t>10:23:28</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       <c r="E87" s="13" t="inlineStr"/>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>22:17:24</t>
+          <t>10:23:34</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       <c r="E88" s="13" t="inlineStr"/>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>22:17:26</t>
+          <t>10:23:36</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       <c r="E89" s="13" t="inlineStr"/>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>22:17:29</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22712,7 @@
       <c r="E90" s="13" t="inlineStr"/>
       <c r="F90" s="13" t="inlineStr">
         <is>
-          <t>22:17:29</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -22740,7 +22740,7 @@
       <c r="E91" s="13" t="inlineStr"/>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:39</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       <c r="E92" s="13" t="inlineStr"/>
       <c r="F92" s="13" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
       <c r="E93" s="13" t="inlineStr"/>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -22824,7 +22824,7 @@
       <c r="E94" s="13" t="inlineStr"/>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>22:17:30</t>
+          <t>10:23:40</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       <c r="E95" s="13" t="inlineStr"/>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>22:17:36</t>
+          <t>10:23:45</t>
         </is>
       </c>
     </row>
@@ -22880,7 +22880,7 @@
       <c r="E96" s="13" t="inlineStr"/>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>22:17:38</t>
+          <t>10:23:48</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       <c r="E97" s="13" t="inlineStr"/>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>22:17:51</t>
+          <t>10:23:58</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       <c r="E98" s="13" t="inlineStr"/>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>22:17:51</t>
+          <t>10:23:58</t>
         </is>
       </c>
     </row>
@@ -22964,7 +22964,7 @@
       <c r="E99" s="13" t="inlineStr"/>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -22992,7 +22992,7 @@
       <c r="E100" s="13" t="inlineStr"/>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23020,7 @@
       <c r="E101" s="13" t="inlineStr"/>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       <c r="E102" s="13" t="inlineStr"/>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23076,7 @@
       <c r="E103" s="13" t="inlineStr"/>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23104,7 +23104,7 @@
       <c r="E104" s="13" t="inlineStr"/>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23132,7 @@
       <c r="E105" s="13" t="inlineStr"/>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>22:17:52</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23160,7 +23160,7 @@
       <c r="E106" s="13" t="inlineStr"/>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>22:17:53</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       <c r="E107" s="13" t="inlineStr"/>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>22:17:53</t>
+          <t>10:23:59</t>
         </is>
       </c>
     </row>
@@ -23216,7 +23216,7 @@
       <c r="E108" s="13" t="inlineStr"/>
       <c r="F108" s="13" t="inlineStr">
         <is>
-          <t>22:18:03</t>
+          <t>10:24:10</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
       <c r="E109" s="13" t="inlineStr"/>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>22:18:03</t>
+          <t>10:24:10</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       <c r="E110" s="13" t="inlineStr"/>
       <c r="F110" s="13" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23300,7 +23300,7 @@
       <c r="E111" s="13" t="inlineStr"/>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23328,7 @@
       <c r="E112" s="13" t="inlineStr"/>
       <c r="F112" s="13" t="inlineStr">
         <is>
-          <t>22:18:13</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23356,7 +23356,7 @@
       <c r="E113" s="13" t="inlineStr"/>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       <c r="E114" s="13" t="inlineStr"/>
       <c r="F114" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       <c r="E115" s="13" t="inlineStr"/>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:20</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       <c r="E116" s="13" t="inlineStr"/>
       <c r="F116" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23468,7 +23468,7 @@
       <c r="E117" s="13" t="inlineStr"/>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23496,7 +23496,7 @@
       <c r="E118" s="13" t="inlineStr"/>
       <c r="F118" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
       <c r="E119" s="13" t="inlineStr"/>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23552,7 +23552,7 @@
       <c r="E120" s="13" t="inlineStr"/>
       <c r="F120" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       <c r="E121" s="13" t="inlineStr"/>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>22:18:14</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       <c r="E122" s="13" t="inlineStr"/>
       <c r="F122" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23636,7 @@
       <c r="E123" s="13" t="inlineStr"/>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:21</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       <c r="E124" s="13" t="inlineStr"/>
       <c r="F124" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       <c r="E125" s="13" t="inlineStr"/>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23720,7 +23720,7 @@
       <c r="E126" s="13" t="inlineStr"/>
       <c r="F126" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23748,7 @@
       <c r="E127" s="13" t="inlineStr"/>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23776,7 @@
       <c r="E128" s="13" t="inlineStr"/>
       <c r="F128" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
       <c r="E129" s="13" t="inlineStr"/>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>22:18:15</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23832,7 +23832,7 @@
       <c r="E130" s="13" t="inlineStr"/>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       <c r="E131" s="13" t="inlineStr"/>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       <c r="E132" s="13" t="inlineStr"/>
       <c r="F132" s="13" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:22</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       <c r="E133" s="13" t="inlineStr"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>22:18:16</t>
+          <t>10:24:23</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       <c r="E134" s="13" t="inlineStr"/>
       <c r="F134" s="13" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -23972,7 +23972,7 @@
       <c r="E135" s="13" t="inlineStr"/>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24000,7 +24000,7 @@
       <c r="E136" s="13" t="inlineStr"/>
       <c r="F136" s="13" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24028,7 +24028,7 @@
       <c r="E137" s="13" t="inlineStr"/>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>22:18:19</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24056,7 +24056,7 @@
       <c r="E138" s="13" t="inlineStr"/>
       <c r="F138" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       <c r="E139" s="13" t="inlineStr"/>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24112,7 +24112,7 @@
       <c r="E140" s="13" t="inlineStr"/>
       <c r="F140" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:26</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
       <c r="E141" s="13" t="inlineStr"/>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24168,7 @@
       <c r="E142" s="13" t="inlineStr"/>
       <c r="F142" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24196,7 +24196,7 @@
       <c r="E143" s="13" t="inlineStr"/>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>22:18:20</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24224,7 +24224,7 @@
       <c r="E144" s="13" t="inlineStr"/>
       <c r="F144" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24252,7 @@
       <c r="E145" s="13" t="inlineStr"/>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       <c r="E146" s="13" t="inlineStr"/>
       <c r="F146" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24308,7 +24308,7 @@
       <c r="E147" s="13" t="inlineStr"/>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24336,7 +24336,7 @@
       <c r="E148" s="13" t="inlineStr"/>
       <c r="F148" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:27</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       <c r="E149" s="13" t="inlineStr"/>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>22:18:21</t>
+          <t>10:24:28</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24392,7 @@
       <c r="E150" s="13" t="inlineStr"/>
       <c r="F150" s="13" t="inlineStr">
         <is>
-          <t>22:18:22</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       <c r="E151" s="13" t="inlineStr"/>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>22:18:22</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       <c r="E152" s="13" t="inlineStr"/>
       <c r="F152" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24476,7 @@
       <c r="E153" s="13" t="inlineStr"/>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24504,7 +24504,7 @@
       <c r="E154" s="13" t="inlineStr"/>
       <c r="F154" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24532,7 @@
       <c r="E155" s="13" t="inlineStr"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24560,7 +24560,7 @@
       <c r="E156" s="13" t="inlineStr"/>
       <c r="F156" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:29</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       <c r="E157" s="13" t="inlineStr"/>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
       <c r="E158" s="13" t="inlineStr"/>
       <c r="F158" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24644,7 +24644,7 @@
       <c r="E159" s="13" t="inlineStr"/>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>22:18:23</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
       <c r="E160" s="13" t="inlineStr"/>
       <c r="F160" s="13" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24700,7 +24700,7 @@
       <c r="E161" s="13" t="inlineStr"/>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
       <c r="E162" s="13" t="inlineStr"/>
       <c r="F162" s="13" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
       <c r="E163" s="13" t="inlineStr"/>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>22:18:24</t>
+          <t>10:24:30</t>
         </is>
       </c>
     </row>
@@ -24784,7 +24784,7 @@
       <c r="E164" s="13" t="inlineStr"/>
       <c r="F164" s="13" t="inlineStr">
         <is>
-          <t>22:18:25</t>
+          <t>10:24:31</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       <c r="E165" s="13" t="inlineStr"/>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>22:18:25</t>
+          <t>10:24:32</t>
         </is>
       </c>
     </row>
@@ -24840,7 +24840,7 @@
       <c r="E166" s="13" t="inlineStr"/>
       <c r="F166" s="13" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -24868,7 +24868,7 @@
       <c r="E167" s="13" t="inlineStr"/>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       <c r="E168" s="13" t="inlineStr"/>
       <c r="F168" s="13" t="inlineStr">
         <is>
-          <t>22:18:28</t>
+          <t>10:24:35</t>
         </is>
       </c>
     </row>
@@ -24924,7 +24924,7 @@
       <c r="E169" s="13" t="inlineStr"/>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -24952,7 +24952,7 @@
       <c r="E170" s="13" t="inlineStr"/>
       <c r="F170" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -24980,7 +24980,7 @@
       <c r="E171" s="13" t="inlineStr"/>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -25008,7 +25008,7 @@
       <c r="E172" s="13" t="inlineStr"/>
       <c r="F172" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -25036,7 +25036,7 @@
       <c r="E173" s="13" t="inlineStr"/>
       <c r="F173" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:36</t>
         </is>
       </c>
     </row>
@@ -25064,7 +25064,7 @@
       <c r="E174" s="13" t="inlineStr"/>
       <c r="F174" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25092,7 +25092,7 @@
       <c r="E175" s="13" t="inlineStr"/>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25120,7 @@
       <c r="E176" s="13" t="inlineStr"/>
       <c r="F176" s="13" t="inlineStr">
         <is>
-          <t>22:18:30</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25148,7 @@
       <c r="E177" s="13" t="inlineStr"/>
       <c r="F177" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       <c r="E178" s="13" t="inlineStr"/>
       <c r="F178" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25204,7 @@
       <c r="E179" s="13" t="inlineStr"/>
       <c r="F179" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       <c r="E180" s="13" t="inlineStr"/>
       <c r="F180" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25260,7 +25260,7 @@
       <c r="E181" s="13" t="inlineStr"/>
       <c r="F181" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:37</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       <c r="E182" s="13" t="inlineStr"/>
       <c r="F182" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25316,7 @@
       <c r="E183" s="13" t="inlineStr"/>
       <c r="F183" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25344,7 +25344,7 @@
       <c r="E184" s="13" t="inlineStr"/>
       <c r="F184" s="13" t="inlineStr">
         <is>
-          <t>22:18:31</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       <c r="E185" s="13" t="inlineStr"/>
       <c r="F185" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25400,7 +25400,7 @@
       <c r="E186" s="13" t="inlineStr"/>
       <c r="F186" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       <c r="E187" s="13" t="inlineStr"/>
       <c r="F187" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       <c r="E188" s="13" t="inlineStr"/>
       <c r="F188" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25484,7 @@
       <c r="E189" s="13" t="inlineStr"/>
       <c r="F189" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       <c r="E190" s="13" t="inlineStr"/>
       <c r="F190" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:38</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
       <c r="E191" s="13" t="inlineStr"/>
       <c r="F191" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -25568,7 +25568,7 @@
       <c r="E192" s="13" t="inlineStr"/>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -25596,7 +25596,7 @@
       <c r="E193" s="13" t="inlineStr"/>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>22:18:32</t>
+          <t>10:24:39</t>
         </is>
       </c>
     </row>
@@ -25624,7 +25624,7 @@
       <c r="E194" s="13" t="inlineStr"/>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -25652,7 +25652,7 @@
       <c r="E195" s="13" t="inlineStr"/>
       <c r="F195" s="13" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -25680,7 +25680,7 @@
       <c r="E196" s="13" t="inlineStr"/>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -25708,7 +25708,7 @@
       <c r="E197" s="13" t="inlineStr"/>
       <c r="F197" s="13" t="inlineStr">
         <is>
-          <t>22:18:34</t>
+          <t>10:24:40</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       <c r="E198" s="13" t="inlineStr"/>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:43</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       <c r="E199" s="13" t="inlineStr"/>
       <c r="F199" s="13" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:43</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
       <c r="E200" s="13" t="inlineStr"/>
       <c r="F200" s="13" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25820,7 +25820,7 @@
       <c r="E201" s="13" t="inlineStr"/>
       <c r="F201" s="13" t="inlineStr">
         <is>
-          <t>22:18:37</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25848,7 +25848,7 @@
       <c r="E202" s="13" t="inlineStr"/>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25876,7 +25876,7 @@
       <c r="E203" s="13" t="inlineStr"/>
       <c r="F203" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25904,7 @@
       <c r="E204" s="13" t="inlineStr"/>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       <c r="E205" s="13" t="inlineStr"/>
       <c r="F205" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       <c r="E206" s="13" t="inlineStr"/>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       <c r="E207" s="13" t="inlineStr"/>
       <c r="F207" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:44</t>
         </is>
       </c>
     </row>
@@ -26016,7 +26016,7 @@
       <c r="E208" s="13" t="inlineStr"/>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       <c r="E209" s="13" t="inlineStr"/>
       <c r="F209" s="13" t="inlineStr">
         <is>
-          <t>22:18:38</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26072,7 @@
       <c r="E210" s="13" t="inlineStr"/>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26100,7 +26100,7 @@
       <c r="E211" s="13" t="inlineStr"/>
       <c r="F211" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26128,7 +26128,7 @@
       <c r="E212" s="13" t="inlineStr"/>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26156,7 +26156,7 @@
       <c r="E213" s="13" t="inlineStr"/>
       <c r="F213" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       <c r="E214" s="13" t="inlineStr"/>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26212,7 +26212,7 @@
       <c r="E215" s="13" t="inlineStr"/>
       <c r="F215" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:45</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       <c r="E216" s="13" t="inlineStr"/>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26268,7 +26268,7 @@
       <c r="E217" s="13" t="inlineStr"/>
       <c r="F217" s="13" t="inlineStr">
         <is>
-          <t>22:18:39</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       <c r="E218" s="13" t="inlineStr"/>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26324,7 +26324,7 @@
       <c r="E219" s="13" t="inlineStr"/>
       <c r="F219" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26352,7 +26352,7 @@
       <c r="E220" s="13" t="inlineStr"/>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26380,7 @@
       <c r="E221" s="13" t="inlineStr"/>
       <c r="F221" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26408,7 @@
       <c r="E222" s="13" t="inlineStr"/>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26436,7 +26436,7 @@
       <c r="E223" s="13" t="inlineStr"/>
       <c r="F223" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26464,7 @@
       <c r="E224" s="13" t="inlineStr"/>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:46</t>
         </is>
       </c>
     </row>
@@ -26492,7 +26492,7 @@
       <c r="E225" s="13" t="inlineStr"/>
       <c r="F225" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26520,7 @@
       <c r="E226" s="13" t="inlineStr"/>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>22:18:40</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       <c r="E227" s="13" t="inlineStr"/>
       <c r="F227" s="13" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
       <c r="E228" s="13" t="inlineStr"/>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -26604,7 +26604,7 @@
       <c r="E229" s="13" t="inlineStr"/>
       <c r="F229" s="13" t="inlineStr">
         <is>
-          <t>22:18:41</t>
+          <t>10:24:47</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
       <c r="E230" s="13" t="inlineStr"/>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26660,7 @@
       <c r="E231" s="13" t="inlineStr"/>
       <c r="F231" s="13" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       <c r="E232" s="13" t="inlineStr"/>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       <c r="E233" s="13" t="inlineStr"/>
       <c r="F233" s="13" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:50</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26744,7 @@
       <c r="E234" s="13" t="inlineStr"/>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>22:18:44</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26772,7 +26772,7 @@
       <c r="E235" s="13" t="inlineStr"/>
       <c r="F235" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26800,7 +26800,7 @@
       <c r="E236" s="13" t="inlineStr"/>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26828,7 +26828,7 @@
       <c r="E237" s="13" t="inlineStr"/>
       <c r="F237" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26856,7 +26856,7 @@
       <c r="E238" s="13" t="inlineStr"/>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26884,7 +26884,7 @@
       <c r="E239" s="13" t="inlineStr"/>
       <c r="F239" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26912,7 +26912,7 @@
       <c r="E240" s="13" t="inlineStr"/>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
       <c r="E241" s="13" t="inlineStr"/>
       <c r="F241" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26968,7 +26968,7 @@
       <c r="E242" s="13" t="inlineStr"/>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:51</t>
         </is>
       </c>
     </row>
@@ -26996,7 +26996,7 @@
       <c r="E243" s="13" t="inlineStr"/>
       <c r="F243" s="13" t="inlineStr">
         <is>
-          <t>22:18:45</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       <c r="E244" s="13" t="inlineStr"/>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27052,7 +27052,7 @@
       <c r="E245" s="13" t="inlineStr"/>
       <c r="F245" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27080,7 +27080,7 @@
       <c r="E246" s="13" t="inlineStr"/>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27108,7 +27108,7 @@
       <c r="E247" s="13" t="inlineStr"/>
       <c r="F247" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       <c r="E248" s="13" t="inlineStr"/>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27164,7 @@
       <c r="E249" s="13" t="inlineStr"/>
       <c r="F249" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27192,7 +27192,7 @@
       <c r="E250" s="13" t="inlineStr"/>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27220,7 @@
       <c r="E251" s="13" t="inlineStr"/>
       <c r="F251" s="13" t="inlineStr">
         <is>
-          <t>22:18:46</t>
+          <t>10:24:52</t>
         </is>
       </c>
     </row>
@@ -27248,7 +27248,7 @@
       <c r="E252" s="13" t="inlineStr"/>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -27276,7 +27276,7 @@
       <c r="E253" s="13" t="inlineStr"/>
       <c r="F253" s="13" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -27304,7 +27304,7 @@
       <c r="E254" s="13" t="inlineStr"/>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -27332,7 +27332,7 @@
       <c r="E255" s="13" t="inlineStr"/>
       <c r="F255" s="13" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -27360,7 +27360,7 @@
       <c r="E256" s="13" t="inlineStr"/>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>22:18:47</t>
+          <t>10:24:53</t>
         </is>
       </c>
     </row>
@@ -27388,7 +27388,7 @@
       <c r="E257" s="13" t="inlineStr"/>
       <c r="F257" s="13" t="inlineStr">
         <is>
-          <t>22:18:50</t>
+          <t>10:24:56</t>
         </is>
       </c>
     </row>
@@ -27416,7 +27416,7 @@
       <c r="E258" s="13" t="inlineStr"/>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>22:18:53</t>
+          <t>10:24:59</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       <c r="E259" s="13" t="inlineStr"/>
       <c r="F259" s="13" t="inlineStr">
         <is>
-          <t>22:18:53</t>
+          <t>10:24:59</t>
         </is>
       </c>
     </row>
@@ -27472,7 +27472,7 @@
       <c r="E260" s="13" t="inlineStr"/>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>22:18:54</t>
+          <t>10:25:00</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       <c r="E261" s="13" t="inlineStr"/>
       <c r="F261" s="13" t="inlineStr">
         <is>
-          <t>22:18:54</t>
+          <t>10:25:00</t>
         </is>
       </c>
     </row>
@@ -27528,7 +27528,7 @@
       <c r="E262" s="13" t="inlineStr"/>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27556,7 +27556,7 @@
       <c r="E263" s="13" t="inlineStr"/>
       <c r="F263" s="13" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27584,7 +27584,7 @@
       <c r="E264" s="13" t="inlineStr"/>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27612,7 +27612,7 @@
       <c r="E265" s="13" t="inlineStr"/>
       <c r="F265" s="13" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27640,7 @@
       <c r="E266" s="13" t="inlineStr"/>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>22:18:56</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       <c r="E267" s="13" t="inlineStr"/>
       <c r="F267" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:02</t>
         </is>
       </c>
     </row>
@@ -27696,7 +27696,7 @@
       <c r="E268" s="13" t="inlineStr"/>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27724,7 +27724,7 @@
       <c r="E269" s="13" t="inlineStr"/>
       <c r="F269" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27752,7 +27752,7 @@
       <c r="E270" s="13" t="inlineStr"/>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27780,7 @@
       <c r="E271" s="13" t="inlineStr"/>
       <c r="F271" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27808,7 +27808,7 @@
       <c r="E272" s="13" t="inlineStr"/>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27836,7 @@
       <c r="E273" s="13" t="inlineStr"/>
       <c r="F273" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27864,7 +27864,7 @@
       <c r="E274" s="13" t="inlineStr"/>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>22:18:57</t>
+          <t>10:25:03</t>
         </is>
       </c>
     </row>
@@ -27892,7 +27892,7 @@
       <c r="E275" s="13" t="inlineStr"/>
       <c r="F275" s="13" t="inlineStr">
         <is>
-          <t>22:19:01</t>
+          <t>10:25:06</t>
         </is>
       </c>
     </row>
@@ -27920,7 +27920,7 @@
       <c r="E276" s="13" t="inlineStr"/>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>22:19:01</t>
+          <t>10:25:07</t>
         </is>
       </c>
     </row>
@@ -27948,7 +27948,7 @@
       <c r="E277" s="13" t="inlineStr"/>
       <c r="F277" s="13" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -27976,7 +27976,7 @@
       <c r="E278" s="13" t="inlineStr"/>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       <c r="E279" s="13" t="inlineStr"/>
       <c r="F279" s="13" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28032,7 +28032,7 @@
       <c r="E280" s="13" t="inlineStr"/>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28060,7 +28060,7 @@
       <c r="E281" s="13" t="inlineStr"/>
       <c r="F281" s="13" t="inlineStr">
         <is>
-          <t>22:19:03</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28088,7 @@
       <c r="E282" s="13" t="inlineStr"/>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>22:19:04</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28116,7 +28116,7 @@
       <c r="E283" s="13" t="inlineStr"/>
       <c r="F283" s="13" t="inlineStr">
         <is>
-          <t>22:19:04</t>
+          <t>10:25:09</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28144,7 @@
       <c r="E284" s="13" t="inlineStr"/>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28172,7 @@
       <c r="E285" s="13" t="inlineStr"/>
       <c r="F285" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       <c r="E286" s="13" t="inlineStr"/>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
       <c r="E287" s="13" t="inlineStr"/>
       <c r="F287" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -28256,7 +28256,7 @@
       <c r="E288" s="13" t="inlineStr"/>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:13</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28284,7 @@
       <c r="E289" s="13" t="inlineStr"/>
       <c r="F289" s="13" t="inlineStr">
         <is>
-          <t>22:19:07</t>
+          <t>10:25:14</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28312,7 @@
       <c r="E290" s="13" t="inlineStr"/>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:14</t>
         </is>
       </c>
     </row>
@@ -28340,7 +28340,7 @@
       <c r="E291" s="13" t="inlineStr"/>
       <c r="F291" s="13" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:16</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       <c r="E292" s="13" t="inlineStr"/>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>22:19:08</t>
+          <t>10:25:17</t>
         </is>
       </c>
     </row>
@@ -28396,7 +28396,7 @@
       <c r="E293" s="13" t="inlineStr"/>
       <c r="F293" s="13" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:18</t>
         </is>
       </c>
     </row>
@@ -28424,7 +28424,7 @@
       <c r="E294" s="13" t="inlineStr"/>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:18</t>
         </is>
       </c>
     </row>
@@ -28452,7 +28452,7 @@
       <c r="E295" s="13" t="inlineStr"/>
       <c r="F295" s="13" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28480,7 @@
       <c r="E296" s="13" t="inlineStr"/>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -28508,7 +28508,7 @@
       <c r="E297" s="13" t="inlineStr"/>
       <c r="F297" s="13" t="inlineStr">
         <is>
-          <t>22:19:09</t>
+          <t>10:25:19</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       <c r="E298" s="13" t="inlineStr"/>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>22:19:10</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
       <c r="E299" s="13" t="inlineStr"/>
       <c r="F299" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -28592,7 +28592,7 @@
       <c r="E300" s="13" t="inlineStr"/>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -28620,7 +28620,7 @@
       <c r="E301" s="13" t="inlineStr"/>
       <c r="F301" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:20</t>
         </is>
       </c>
     </row>
@@ -28648,7 +28648,7 @@
       <c r="E302" s="13" t="inlineStr"/>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -28676,7 +28676,7 @@
       <c r="E303" s="13" t="inlineStr"/>
       <c r="F303" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -28704,7 +28704,7 @@
       <c r="E304" s="13" t="inlineStr"/>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -28732,7 +28732,7 @@
       <c r="E305" s="13" t="inlineStr"/>
       <c r="F305" s="13" t="inlineStr">
         <is>
-          <t>22:19:11</t>
+          <t>10:25:21</t>
         </is>
       </c>
     </row>
@@ -28760,7 +28760,7 @@
       <c r="E306" s="13" t="inlineStr"/>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>22:19:14</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -28788,7 +28788,7 @@
       <c r="E307" s="13" t="inlineStr"/>
       <c r="F307" s="13" t="inlineStr">
         <is>
-          <t>22:19:14</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -28816,7 +28816,7 @@
       <c r="E308" s="13" t="inlineStr"/>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28844,7 @@
       <c r="E309" s="13" t="inlineStr"/>
       <c r="F309" s="13" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:24</t>
         </is>
       </c>
     </row>
@@ -28872,7 +28872,7 @@
       <c r="E310" s="13" t="inlineStr"/>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:25</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       <c r="E311" s="13" t="inlineStr"/>
       <c r="F311" s="13" t="inlineStr">
         <is>
-          <t>22:19:15</t>
+          <t>10:25:25</t>
         </is>
       </c>
     </row>
@@ -28928,7 +28928,7 @@
       <c r="E312" s="13" t="inlineStr"/>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -28956,7 +28956,7 @@
       <c r="E313" s="13" t="inlineStr"/>
       <c r="F313" s="13" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -28984,7 +28984,7 @@
       <c r="E314" s="13" t="inlineStr"/>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -29012,7 +29012,7 @@
       <c r="E315" s="13" t="inlineStr"/>
       <c r="F315" s="13" t="inlineStr">
         <is>
-          <t>22:19:16</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -29040,7 +29040,7 @@
       <c r="E316" s="13" t="inlineStr"/>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>22:19:17</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29068,7 @@
       <c r="E317" s="13" t="inlineStr"/>
       <c r="F317" s="13" t="inlineStr">
         <is>
-          <t>22:19:17</t>
+          <t>10:25:26</t>
         </is>
       </c>
     </row>
@@ -29096,7 +29096,7 @@
       <c r="E318" s="13" t="inlineStr"/>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29124,7 @@
       <c r="E319" s="13" t="inlineStr"/>
       <c r="F319" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29152,7 +29152,7 @@
       <c r="E320" s="13" t="inlineStr"/>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29180,7 @@
       <c r="E321" s="13" t="inlineStr"/>
       <c r="F321" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29208,7 +29208,7 @@
       <c r="E322" s="13" t="inlineStr"/>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29236,7 +29236,7 @@
       <c r="E323" s="13" t="inlineStr"/>
       <c r="F323" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29264,7 +29264,7 @@
       <c r="E324" s="13" t="inlineStr"/>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>22:19:18</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29292,7 @@
       <c r="E325" s="13" t="inlineStr"/>
       <c r="F325" s="13" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29320,7 +29320,7 @@
       <c r="E326" s="13" t="inlineStr"/>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:28</t>
         </is>
       </c>
     </row>
@@ -29348,7 +29348,7 @@
       <c r="E327" s="13" t="inlineStr"/>
       <c r="F327" s="13" t="inlineStr">
         <is>
-          <t>22:19:19</t>
+          <t>10:25:29</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
       <c r="E328" s="13" t="inlineStr"/>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -29404,7 +29404,7 @@
       <c r="E329" s="13" t="inlineStr"/>
       <c r="F329" s="13" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -29432,7 +29432,7 @@
       <c r="E330" s="13" t="inlineStr"/>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -29460,7 +29460,7 @@
       <c r="E331" s="13" t="inlineStr"/>
       <c r="F331" s="13" t="inlineStr">
         <is>
-          <t>22:19:22</t>
+          <t>10:25:32</t>
         </is>
       </c>
     </row>
@@ -29488,7 +29488,7 @@
       <c r="E332" s="13" t="inlineStr"/>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>22:19:23</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -29516,7 +29516,7 @@
       <c r="E333" s="13" t="inlineStr"/>
       <c r="F333" s="13" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -29544,7 +29544,7 @@
       <c r="E334" s="13" t="inlineStr"/>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:33</t>
         </is>
       </c>
     </row>
@@ -29572,7 +29572,7 @@
       <c r="E335" s="13" t="inlineStr"/>
       <c r="F335" s="13" t="inlineStr">
         <is>
-          <t>22:19:24</t>
+          <t>10:25:34</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29600,7 @@
       <c r="E336" s="13" t="inlineStr"/>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -29628,7 +29628,7 @@
       <c r="E337" s="13" t="inlineStr"/>
       <c r="F337" s="13" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29656,7 @@
       <c r="E338" s="13" t="inlineStr"/>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -29684,7 +29684,7 @@
       <c r="E339" s="13" t="inlineStr"/>
       <c r="F339" s="13" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       <c r="E340" s="13" t="inlineStr"/>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>22:19:25</t>
+          <t>10:25:35</t>
         </is>
       </c>
     </row>
@@ -29740,7 +29740,7 @@
       <c r="E341" s="13" t="inlineStr"/>
       <c r="F341" s="13" t="inlineStr">
         <is>
-          <t>22:19:27</t>
+          <t>10:25:36</t>
         </is>
       </c>
     </row>
@@ -29768,7 +29768,7 @@
       <c r="E342" s="13" t="inlineStr"/>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>22:19:27</t>
+          <t>10:25:36</t>
         </is>
       </c>
     </row>
@@ -29796,7 +29796,7 @@
       <c r="E343" s="13" t="inlineStr"/>
       <c r="F343" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:37</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       <c r="E344" s="13" t="inlineStr"/>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -29852,7 +29852,7 @@
       <c r="E345" s="13" t="inlineStr"/>
       <c r="F345" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -29880,7 +29880,7 @@
       <c r="E346" s="13" t="inlineStr"/>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -29908,7 +29908,7 @@
       <c r="E347" s="13" t="inlineStr"/>
       <c r="F347" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -29936,7 +29936,7 @@
       <c r="E348" s="13" t="inlineStr"/>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>22:19:28</t>
+          <t>10:25:38</t>
         </is>
       </c>
     </row>
@@ -29964,7 +29964,7 @@
       <c r="E349" s="13" t="inlineStr"/>
       <c r="F349" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -29992,7 +29992,7 @@
       <c r="E350" s="13" t="inlineStr"/>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -30020,7 +30020,7 @@
       <c r="E351" s="13" t="inlineStr"/>
       <c r="F351" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:41</t>
         </is>
       </c>
     </row>
@@ -30048,7 +30048,7 @@
       <c r="E352" s="13" t="inlineStr"/>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -30076,7 +30076,7 @@
       <c r="E353" s="13" t="inlineStr"/>
       <c r="F353" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30104,7 @@
       <c r="E354" s="13" t="inlineStr"/>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>22:19:32</t>
+          <t>10:25:42</t>
         </is>
       </c>
     </row>
@@ -30132,7 +30132,7 @@
       <c r="E355" s="13" t="inlineStr"/>
       <c r="F355" s="13" t="inlineStr">
         <is>
-          <t>22:19:33</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30160,7 +30160,7 @@
       <c r="E356" s="13" t="inlineStr"/>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>22:19:33</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30188,7 +30188,7 @@
       <c r="E357" s="13" t="inlineStr"/>
       <c r="F357" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30216,7 @@
       <c r="E358" s="13" t="inlineStr"/>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30244,7 +30244,7 @@
       <c r="E359" s="13" t="inlineStr"/>
       <c r="F359" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30272,7 +30272,7 @@
       <c r="E360" s="13" t="inlineStr"/>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:43</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30300,7 @@
       <c r="E361" s="13" t="inlineStr"/>
       <c r="F361" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -30328,7 +30328,7 @@
       <c r="E362" s="13" t="inlineStr"/>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -30356,7 +30356,7 @@
       <c r="E363" s="13" t="inlineStr"/>
       <c r="F363" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -30384,7 +30384,7 @@
       <c r="E364" s="13" t="inlineStr"/>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>22:19:34</t>
+          <t>10:25:44</t>
         </is>
       </c>
     </row>
@@ -30412,7 +30412,7 @@
       <c r="E365" s="13" t="inlineStr"/>
       <c r="F365" s="13" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
       <c r="E366" s="13" t="inlineStr"/>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       <c r="E367" s="13" t="inlineStr"/>
       <c r="F367" s="13" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -30496,7 +30496,7 @@
       <c r="E368" s="13" t="inlineStr"/>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:45</t>
         </is>
       </c>
     </row>
@@ -30524,7 +30524,7 @@
       <c r="E369" s="13" t="inlineStr"/>
       <c r="F369" s="13" t="inlineStr">
         <is>
-          <t>22:19:36</t>
+          <t>10:25:46</t>
         </is>
       </c>
     </row>
@@ -30552,7 +30552,7 @@
       <c r="E370" s="13" t="inlineStr"/>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30580,7 +30580,7 @@
       <c r="E371" s="13" t="inlineStr"/>
       <c r="F371" s="13" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       <c r="E372" s="13" t="inlineStr"/>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>22:19:39</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30636,7 +30636,7 @@
       <c r="E373" s="13" t="inlineStr"/>
       <c r="F373" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
       <c r="E374" s="13" t="inlineStr"/>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30692,7 @@
       <c r="E375" s="13" t="inlineStr"/>
       <c r="F375" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30720,7 +30720,7 @@
       <c r="E376" s="13" t="inlineStr"/>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:49</t>
         </is>
       </c>
     </row>
@@ -30748,7 +30748,7 @@
       <c r="E377" s="13" t="inlineStr"/>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30776,7 +30776,7 @@
       <c r="E378" s="13" t="inlineStr"/>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       <c r="E379" s="13" t="inlineStr"/>
       <c r="F379" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30832,7 +30832,7 @@
       <c r="E380" s="13" t="inlineStr"/>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30860,7 @@
       <c r="E381" s="13" t="inlineStr"/>
       <c r="F381" s="13" t="inlineStr">
         <is>
-          <t>22:19:40</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30888,7 +30888,7 @@
       <c r="E382" s="13" t="inlineStr"/>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30916,7 +30916,7 @@
       <c r="E383" s="13" t="inlineStr"/>
       <c r="F383" s="13" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30944,7 +30944,7 @@
       <c r="E384" s="13" t="inlineStr"/>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:50</t>
         </is>
       </c>
     </row>
@@ -30972,7 +30972,7 @@
       <c r="E385" s="13" t="inlineStr"/>
       <c r="F385" s="13" t="inlineStr">
         <is>
-          <t>22:19:41</t>
+          <t>10:25:51</t>
         </is>
       </c>
     </row>
@@ -31000,7 +31000,7 @@
       <c r="E386" s="13" t="inlineStr"/>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31028,7 +31028,7 @@
       <c r="E387" s="13" t="inlineStr"/>
       <c r="F387" s="13" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31056,7 +31056,7 @@
       <c r="E388" s="13" t="inlineStr"/>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31084,7 +31084,7 @@
       <c r="E389" s="13" t="inlineStr"/>
       <c r="F389" s="13" t="inlineStr">
         <is>
-          <t>22:19:44</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31112,7 @@
       <c r="E390" s="13" t="inlineStr"/>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       <c r="E391" s="13" t="inlineStr"/>
       <c r="F391" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31168,7 +31168,7 @@
       <c r="E392" s="13" t="inlineStr"/>
       <c r="F392" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31196,7 +31196,7 @@
       <c r="E393" s="13" t="inlineStr"/>
       <c r="F393" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:54</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       <c r="E394" s="13" t="inlineStr"/>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31252,7 +31252,7 @@
       <c r="E395" s="13" t="inlineStr"/>
       <c r="F395" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31280,7 @@
       <c r="E396" s="13" t="inlineStr"/>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31308,7 +31308,7 @@
       <c r="E397" s="13" t="inlineStr"/>
       <c r="F397" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31336,7 +31336,7 @@
       <c r="E398" s="13" t="inlineStr"/>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>22:19:45</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31364,7 @@
       <c r="E399" s="13" t="inlineStr"/>
       <c r="F399" s="13" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       <c r="E400" s="13" t="inlineStr"/>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       <c r="E401" s="13" t="inlineStr"/>
       <c r="F401" s="13" t="inlineStr">
         <is>
-          <t>22:19:46</t>
+          <t>10:25:55</t>
         </is>
       </c>
     </row>
